--- a/research/traditional_assets/database/data/israel/israel_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_computers_peripherals.xlsx
@@ -1382,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1519,22 +1519,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1264030567664124</v>
+        <v>0.1261469797358497</v>
       </c>
       <c r="C2">
-        <v>24.5</v>
+        <v>24.27763241481832</v>
       </c>
       <c r="D2">
-        <v>16.02</v>
+        <v>16.04263241481832</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="G2">
         <v>8.48</v>
@@ -1555,28 +1555,28 @@
         <v>4.15</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0123235</v>
       </c>
       <c r="N2">
-        <v>4.15</v>
+        <v>4.1376765</v>
       </c>
       <c r="O2">
-        <v>0.9545000000000001</v>
+        <v>0.9516655950000001</v>
       </c>
       <c r="P2">
-        <v>3.1955</v>
+        <v>3.186010905</v>
       </c>
       <c r="Q2">
-        <v>3.9655</v>
+        <v>3.956010905</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1264030567664124</v>
+        <v>0.1270299694301512</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.256601792858447</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>336.7549803221488</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1601,22 +1601,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1261469797358497</v>
+        <v>0.1258909027052869</v>
       </c>
       <c r="C3">
-        <v>24.27763241481832</v>
+        <v>24.05532886844775</v>
       </c>
       <c r="D3">
-        <v>16.04263241481832</v>
+        <v>16.06532886844775</v>
       </c>
       <c r="E3">
-        <v>0.245</v>
+        <v>0.49</v>
       </c>
       <c r="F3">
-        <v>0.245</v>
+        <v>0.49</v>
       </c>
       <c r="G3">
         <v>8.48</v>
@@ -1637,28 +1637,28 @@
         <v>4.15</v>
       </c>
       <c r="M3">
-        <v>0.0123235</v>
+        <v>0.024647</v>
       </c>
       <c r="N3">
-        <v>4.1376765</v>
+        <v>4.125353</v>
       </c>
       <c r="O3">
-        <v>0.9516655950000001</v>
+        <v>0.9488311900000002</v>
       </c>
       <c r="P3">
-        <v>3.186010905</v>
+        <v>3.176521810000001</v>
       </c>
       <c r="Q3">
-        <v>3.956010905</v>
+        <v>3.94652181</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1270299694301512</v>
+        <v>0.1276696762298846</v>
       </c>
       <c r="T3">
-        <v>1.256601792858447</v>
+        <v>1.266497853599182</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>336.7549803221488</v>
+        <v>168.3774901610744</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1683,22 +1683,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1258909027052869</v>
+        <v>0.1256348256747241</v>
       </c>
       <c r="C4">
-        <v>24.05532886844775</v>
+        <v>23.83308963307176</v>
       </c>
       <c r="D4">
-        <v>16.06532886844775</v>
+        <v>16.08808963307176</v>
       </c>
       <c r="E4">
-        <v>0.49</v>
+        <v>0.735</v>
       </c>
       <c r="F4">
-        <v>0.49</v>
+        <v>0.735</v>
       </c>
       <c r="G4">
         <v>8.48</v>
@@ -1719,28 +1719,28 @@
         <v>4.15</v>
       </c>
       <c r="M4">
-        <v>0.024647</v>
+        <v>0.0369705</v>
       </c>
       <c r="N4">
-        <v>4.125353</v>
+        <v>4.113029500000001</v>
       </c>
       <c r="O4">
-        <v>0.9488311900000002</v>
+        <v>0.9459967850000002</v>
       </c>
       <c r="P4">
-        <v>3.176521810000001</v>
+        <v>3.167032715</v>
       </c>
       <c r="Q4">
-        <v>3.94652181</v>
+        <v>3.937032715</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1276696762298846</v>
+        <v>0.1283225728605404</v>
       </c>
       <c r="T4">
-        <v>1.266497853599182</v>
+        <v>1.276597956829416</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>168.3774901610744</v>
+        <v>112.2516601073829</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1765,22 +1765,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1256348256747241</v>
+        <v>0.1253787486441614</v>
       </c>
       <c r="C5">
-        <v>23.83308963307176</v>
+        <v>23.61091498241847</v>
       </c>
       <c r="D5">
-        <v>16.08808963307176</v>
+        <v>16.11091498241847</v>
       </c>
       <c r="E5">
-        <v>0.735</v>
+        <v>0.98</v>
       </c>
       <c r="F5">
-        <v>0.735</v>
+        <v>0.98</v>
       </c>
       <c r="G5">
         <v>8.48</v>
@@ -1801,28 +1801,28 @@
         <v>4.15</v>
       </c>
       <c r="M5">
-        <v>0.0369705</v>
+        <v>0.049294</v>
       </c>
       <c r="N5">
-        <v>4.113029500000001</v>
+        <v>4.100706000000001</v>
       </c>
       <c r="O5">
-        <v>0.9459967850000002</v>
+        <v>0.9431623800000002</v>
       </c>
       <c r="P5">
-        <v>3.167032715</v>
+        <v>3.15754362</v>
       </c>
       <c r="Q5">
-        <v>3.937032715</v>
+        <v>3.92754362</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1283225728605404</v>
+        <v>0.1289890715043348</v>
       </c>
       <c r="T5">
-        <v>1.276597956829416</v>
+        <v>1.286908478876946</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>112.2516601073829</v>
+        <v>84.1887450805372</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1253787486441614</v>
+        <v>0.1251226716135986</v>
       </c>
       <c r="C6">
-        <v>23.61091498241847</v>
+        <v>23.38880519177167</v>
       </c>
       <c r="D6">
-        <v>16.11091498241847</v>
+        <v>16.13380519177167</v>
       </c>
       <c r="E6">
-        <v>0.98</v>
+        <v>1.225</v>
       </c>
       <c r="F6">
-        <v>0.98</v>
+        <v>1.225</v>
       </c>
       <c r="G6">
         <v>8.48</v>
@@ -1883,28 +1883,28 @@
         <v>4.15</v>
       </c>
       <c r="M6">
-        <v>0.049294</v>
+        <v>0.0616175</v>
       </c>
       <c r="N6">
-        <v>4.100706000000001</v>
+        <v>4.088382500000001</v>
       </c>
       <c r="O6">
-        <v>0.9431623800000002</v>
+        <v>0.9403279750000002</v>
       </c>
       <c r="P6">
-        <v>3.15754362</v>
+        <v>3.148054525</v>
       </c>
       <c r="Q6">
-        <v>3.92754362</v>
+        <v>3.918054525</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1289890715043348</v>
+        <v>0.1296696016985249</v>
       </c>
       <c r="T6">
-        <v>1.286908478876946</v>
+        <v>1.29743606454653</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>84.1887450805372</v>
+        <v>67.35099606442976</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1251226716135986</v>
+        <v>0.1248665945830359</v>
       </c>
       <c r="C7">
-        <v>23.38880519177167</v>
+        <v>23.16676053798184</v>
       </c>
       <c r="D7">
-        <v>16.13380519177167</v>
+        <v>16.15676053798184</v>
       </c>
       <c r="E7">
-        <v>1.225</v>
+        <v>1.47</v>
       </c>
       <c r="F7">
-        <v>1.225</v>
+        <v>1.47</v>
       </c>
       <c r="G7">
         <v>8.48</v>
@@ -1965,28 +1965,28 @@
         <v>4.15</v>
       </c>
       <c r="M7">
-        <v>0.0616175</v>
+        <v>0.07394100000000001</v>
       </c>
       <c r="N7">
-        <v>4.088382500000001</v>
+        <v>4.076059000000001</v>
       </c>
       <c r="O7">
-        <v>0.9403279750000002</v>
+        <v>0.9374935700000002</v>
       </c>
       <c r="P7">
-        <v>3.148054525</v>
+        <v>3.138565430000001</v>
       </c>
       <c r="Q7">
-        <v>3.918054525</v>
+        <v>3.90856543</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1296696016985249</v>
+        <v>0.1303646112585488</v>
       </c>
       <c r="T7">
-        <v>1.29743606454653</v>
+        <v>1.308187641400573</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>67.35099606442976</v>
+        <v>56.12583005369146</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2011,22 +2011,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1248665945830359</v>
+        <v>0.1246105175524731</v>
       </c>
       <c r="C8">
-        <v>23.16676053798184</v>
+        <v>22.94478129947731</v>
       </c>
       <c r="D8">
-        <v>16.15676053798184</v>
+        <v>16.17978129947731</v>
       </c>
       <c r="E8">
-        <v>1.47</v>
+        <v>1.715</v>
       </c>
       <c r="F8">
-        <v>1.47</v>
+        <v>1.715</v>
       </c>
       <c r="G8">
         <v>8.48</v>
@@ -2047,28 +2047,28 @@
         <v>4.15</v>
       </c>
       <c r="M8">
-        <v>0.07394099999999999</v>
+        <v>0.08626449999999999</v>
       </c>
       <c r="N8">
-        <v>4.076059000000001</v>
+        <v>4.0637355</v>
       </c>
       <c r="O8">
-        <v>0.9374935700000002</v>
+        <v>0.934659165</v>
       </c>
       <c r="P8">
-        <v>3.138565430000001</v>
+        <v>3.129076335</v>
       </c>
       <c r="Q8">
-        <v>3.90856543</v>
+        <v>3.899076334999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1303646112585488</v>
+        <v>0.1310745672607238</v>
       </c>
       <c r="T8">
-        <v>1.308187641400573</v>
+        <v>1.319170434961155</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>56.12583005369147</v>
+        <v>48.10785433173554</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1246105175524731</v>
+        <v>0.1243544405219104</v>
       </c>
       <c r="C9">
-        <v>22.94478129947731</v>
+        <v>22.72286775627556</v>
       </c>
       <c r="D9">
-        <v>16.17978129947731</v>
+        <v>16.20286775627556</v>
       </c>
       <c r="E9">
-        <v>1.715</v>
+        <v>1.96</v>
       </c>
       <c r="F9">
-        <v>1.715</v>
+        <v>1.96</v>
       </c>
       <c r="G9">
         <v>8.48</v>
@@ -2129,28 +2129,28 @@
         <v>4.15</v>
       </c>
       <c r="M9">
-        <v>0.08626449999999999</v>
+        <v>0.098588</v>
       </c>
       <c r="N9">
-        <v>4.0637355</v>
+        <v>4.051412</v>
       </c>
       <c r="O9">
-        <v>0.934659165</v>
+        <v>0.93182476</v>
       </c>
       <c r="P9">
-        <v>3.129076335</v>
+        <v>3.11958724</v>
       </c>
       <c r="Q9">
-        <v>3.899076334999999</v>
+        <v>3.88958724</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1310745672607238</v>
+        <v>0.131799957089033</v>
       </c>
       <c r="T9">
-        <v>1.319170434961155</v>
+        <v>1.330391984903488</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>48.10785433173554</v>
+        <v>42.09437254026859</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1243544405219104</v>
+        <v>0.1240983634913476</v>
       </c>
       <c r="C10">
-        <v>22.72286775627556</v>
+        <v>22.50102018999456</v>
       </c>
       <c r="D10">
-        <v>16.20286775627556</v>
+        <v>16.22602018999455</v>
       </c>
       <c r="E10">
-        <v>1.96</v>
+        <v>2.205</v>
       </c>
       <c r="F10">
-        <v>1.96</v>
+        <v>2.205</v>
       </c>
       <c r="G10">
         <v>8.48</v>
@@ -2211,28 +2211,28 @@
         <v>4.15</v>
       </c>
       <c r="M10">
-        <v>0.098588</v>
+        <v>0.1109115</v>
       </c>
       <c r="N10">
-        <v>4.051412</v>
+        <v>4.0390885</v>
       </c>
       <c r="O10">
-        <v>0.93182476</v>
+        <v>0.928990355</v>
       </c>
       <c r="P10">
-        <v>3.11958724</v>
+        <v>3.110098145</v>
       </c>
       <c r="Q10">
-        <v>3.88958724</v>
+        <v>3.880098145</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.131799957089033</v>
+        <v>0.1325412895509315</v>
       </c>
       <c r="T10">
-        <v>1.330391984903488</v>
+        <v>1.341860162317082</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.09437254026859</v>
+        <v>37.41722003579431</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1240983634913476</v>
+        <v>0.1238422864607849</v>
       </c>
       <c r="C11">
-        <v>22.50102018999456</v>
+        <v>22.27923888386417</v>
       </c>
       <c r="D11">
-        <v>16.22602018999455</v>
+        <v>16.24923888386417</v>
       </c>
       <c r="E11">
-        <v>2.205</v>
+        <v>2.45</v>
       </c>
       <c r="F11">
-        <v>2.205</v>
+        <v>2.45</v>
       </c>
       <c r="G11">
         <v>8.48</v>
@@ -2293,28 +2293,28 @@
         <v>4.15</v>
       </c>
       <c r="M11">
-        <v>0.1109115</v>
+        <v>0.123235</v>
       </c>
       <c r="N11">
-        <v>4.0390885</v>
+        <v>4.026765</v>
       </c>
       <c r="O11">
-        <v>0.928990355</v>
+        <v>0.9261559500000001</v>
       </c>
       <c r="P11">
-        <v>3.110098145</v>
+        <v>3.10060905</v>
       </c>
       <c r="Q11">
-        <v>3.880098145</v>
+        <v>3.87060905</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1325412895509315</v>
+        <v>0.1332990960675388</v>
       </c>
       <c r="T11">
-        <v>1.341860162317082</v>
+        <v>1.353583188117644</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.41722003579431</v>
+        <v>33.67549803221488</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2339,22 +2339,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1238422864607849</v>
+        <v>0.1235862094302222</v>
       </c>
       <c r="C12">
-        <v>22.27923888386417</v>
+        <v>22.05752412273776</v>
       </c>
       <c r="D12">
-        <v>16.24923888386417</v>
+        <v>16.27252412273776</v>
       </c>
       <c r="E12">
-        <v>2.45</v>
+        <v>2.695</v>
       </c>
       <c r="F12">
-        <v>2.45</v>
+        <v>2.695</v>
       </c>
       <c r="G12">
         <v>8.48</v>
@@ -2375,28 +2375,28 @@
         <v>4.15</v>
       </c>
       <c r="M12">
-        <v>0.123235</v>
+        <v>0.1355585</v>
       </c>
       <c r="N12">
-        <v>4.026765</v>
+        <v>4.0144415</v>
       </c>
       <c r="O12">
-        <v>0.9261559500000001</v>
+        <v>0.9233215450000001</v>
       </c>
       <c r="P12">
-        <v>3.10060905</v>
+        <v>3.091119955</v>
       </c>
       <c r="Q12">
-        <v>3.87060905</v>
+        <v>3.861119954999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1332990960675388</v>
+        <v>0.1340739319440698</v>
       </c>
       <c r="T12">
-        <v>1.353583188117644</v>
+        <v>1.365569652700241</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.67549803221488</v>
+        <v>30.61408912019534</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2421,22 +2421,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1235862094302222</v>
+        <v>0.1233301323996594</v>
       </c>
       <c r="C13">
-        <v>22.05752412273776</v>
+        <v>21.83587619310381</v>
       </c>
       <c r="D13">
-        <v>16.27252412273776</v>
+        <v>16.29587619310382</v>
       </c>
       <c r="E13">
-        <v>2.695</v>
+        <v>2.94</v>
       </c>
       <c r="F13">
-        <v>2.695</v>
+        <v>2.94</v>
       </c>
       <c r="G13">
         <v>8.48</v>
@@ -2457,28 +2457,28 @@
         <v>4.15</v>
       </c>
       <c r="M13">
-        <v>0.1355585</v>
+        <v>0.147882</v>
       </c>
       <c r="N13">
-        <v>4.0144415</v>
+        <v>4.002118</v>
       </c>
       <c r="O13">
-        <v>0.9233215450000001</v>
+        <v>0.9204871400000001</v>
       </c>
       <c r="P13">
-        <v>3.091119955</v>
+        <v>3.08163086</v>
       </c>
       <c r="Q13">
-        <v>3.861119954999999</v>
+        <v>3.85163086</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1340739319440698</v>
+        <v>0.1348663777268857</v>
       </c>
       <c r="T13">
-        <v>1.365569652700241</v>
+        <v>1.377828536932443</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.61408912019534</v>
+        <v>28.06291502684573</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2503,22 +2503,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1233301323996594</v>
+        <v>0.1230740553690966</v>
       </c>
       <c r="C14">
-        <v>21.83587619310381</v>
+        <v>21.61429538309771</v>
       </c>
       <c r="D14">
-        <v>16.29587619310382</v>
+        <v>16.31929538309771</v>
       </c>
       <c r="E14">
-        <v>2.94</v>
+        <v>3.185</v>
       </c>
       <c r="F14">
-        <v>2.94</v>
+        <v>3.185</v>
       </c>
       <c r="G14">
         <v>8.48</v>
@@ -2539,28 +2539,28 @@
         <v>4.15</v>
       </c>
       <c r="M14">
-        <v>0.147882</v>
+        <v>0.1602055</v>
       </c>
       <c r="N14">
-        <v>4.002118</v>
+        <v>3.9897945</v>
       </c>
       <c r="O14">
-        <v>0.9204871400000001</v>
+        <v>0.9176527350000001</v>
       </c>
       <c r="P14">
-        <v>3.08163086</v>
+        <v>3.072141765</v>
       </c>
       <c r="Q14">
-        <v>3.85163086</v>
+        <v>3.842141765</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1348663777268857</v>
+        <v>0.1356770406541341</v>
       </c>
       <c r="T14">
-        <v>1.377828536932443</v>
+        <v>1.39036923459527</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.06291502684573</v>
+        <v>25.9042292555499</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1230740553690966</v>
+        <v>0.1228179783385339</v>
       </c>
       <c r="C15">
-        <v>21.61429538309771</v>
+        <v>21.39278198251353</v>
       </c>
       <c r="D15">
-        <v>16.31929538309771</v>
+        <v>16.34278198251353</v>
       </c>
       <c r="E15">
-        <v>3.185</v>
+        <v>3.43</v>
       </c>
       <c r="F15">
-        <v>3.185</v>
+        <v>3.43</v>
       </c>
       <c r="G15">
         <v>8.48</v>
@@ -2621,28 +2621,28 @@
         <v>4.15</v>
       </c>
       <c r="M15">
-        <v>0.1602055</v>
+        <v>0.172529</v>
       </c>
       <c r="N15">
-        <v>3.9897945</v>
+        <v>3.977471</v>
       </c>
       <c r="O15">
-        <v>0.9176527350000001</v>
+        <v>0.9148183300000001</v>
       </c>
       <c r="P15">
-        <v>3.072141765</v>
+        <v>3.06265267</v>
       </c>
       <c r="Q15">
-        <v>3.842141765</v>
+        <v>3.83265267</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1356770406541341</v>
+        <v>0.1365065562075976</v>
       </c>
       <c r="T15">
-        <v>1.39036923459527</v>
+        <v>1.403201576389791</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.9042292555499</v>
+        <v>24.05392716586777</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2667,22 +2667,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1228179783385339</v>
+        <v>0.1225619013079711</v>
       </c>
       <c r="C16">
-        <v>21.39278198251353</v>
+        <v>21.17133628281605</v>
       </c>
       <c r="D16">
-        <v>16.34278198251353</v>
+        <v>16.36633628281605</v>
       </c>
       <c r="E16">
-        <v>3.43</v>
+        <v>3.675000000000001</v>
       </c>
       <c r="F16">
-        <v>3.43</v>
+        <v>3.675000000000001</v>
       </c>
       <c r="G16">
         <v>8.48</v>
@@ -2703,28 +2703,28 @@
         <v>4.15</v>
       </c>
       <c r="M16">
-        <v>0.172529</v>
+        <v>0.1848525</v>
       </c>
       <c r="N16">
-        <v>3.977471</v>
+        <v>3.9651475</v>
       </c>
       <c r="O16">
-        <v>0.9148183300000001</v>
+        <v>0.9119839250000001</v>
       </c>
       <c r="P16">
-        <v>3.06265267</v>
+        <v>3.053163575</v>
       </c>
       <c r="Q16">
-        <v>3.83265267</v>
+        <v>3.823163575</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1365065562075976</v>
+        <v>0.1373555897740837</v>
       </c>
       <c r="T16">
-        <v>1.403201576389791</v>
+        <v>1.416335855638301</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.05392716586777</v>
+        <v>22.45033202147658</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2749,22 +2749,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1225619013079711</v>
+        <v>0.1223058242774084</v>
       </c>
       <c r="C17">
-        <v>21.17133628281605</v>
+        <v>20.9499585771528</v>
       </c>
       <c r="D17">
-        <v>16.36633628281605</v>
+        <v>16.3899585771528</v>
       </c>
       <c r="E17">
-        <v>3.675</v>
+        <v>3.92</v>
       </c>
       <c r="F17">
-        <v>3.675</v>
+        <v>3.92</v>
       </c>
       <c r="G17">
         <v>8.48</v>
@@ -2785,28 +2785,28 @@
         <v>4.15</v>
       </c>
       <c r="M17">
-        <v>0.1848525</v>
+        <v>0.197176</v>
       </c>
       <c r="N17">
-        <v>3.9651475</v>
+        <v>3.952824000000001</v>
       </c>
       <c r="O17">
-        <v>0.9119839250000001</v>
+        <v>0.9091495200000002</v>
       </c>
       <c r="P17">
-        <v>3.053163575</v>
+        <v>3.04367448</v>
       </c>
       <c r="Q17">
-        <v>3.823163575</v>
+        <v>3.81367448</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1373555897740837</v>
+        <v>0.1382248384254862</v>
       </c>
       <c r="T17">
-        <v>1.416335855638301</v>
+        <v>1.429782855821299</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.45033202147659</v>
+        <v>21.0471862701343</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2831,22 +2831,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1223058242774084</v>
+        <v>0.1220497472468457</v>
       </c>
       <c r="C18">
-        <v>20.9499585771528</v>
+        <v>20.72864916036619</v>
       </c>
       <c r="D18">
-        <v>16.3899585771528</v>
+        <v>16.41364916036618</v>
       </c>
       <c r="E18">
-        <v>3.92</v>
+        <v>4.165</v>
       </c>
       <c r="F18">
-        <v>3.92</v>
+        <v>4.165</v>
       </c>
       <c r="G18">
         <v>8.48</v>
@@ -2867,28 +2867,28 @@
         <v>4.15</v>
       </c>
       <c r="M18">
-        <v>0.197176</v>
+        <v>0.2094995</v>
       </c>
       <c r="N18">
-        <v>3.952824000000001</v>
+        <v>3.9405005</v>
       </c>
       <c r="O18">
-        <v>0.9091495200000002</v>
+        <v>0.9063151150000001</v>
       </c>
       <c r="P18">
-        <v>3.04367448</v>
+        <v>3.034185385</v>
       </c>
       <c r="Q18">
-        <v>3.81367448</v>
+        <v>3.804185385</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1382248384254862</v>
+        <v>0.1391150328275249</v>
       </c>
       <c r="T18">
-        <v>1.429782855821299</v>
+        <v>1.443553880105091</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.0471862701343</v>
+        <v>19.80911648953816</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1220497472468457</v>
+        <v>0.1217936702162829</v>
       </c>
       <c r="C19">
-        <v>20.72864916036619</v>
+        <v>20.50740832900579</v>
       </c>
       <c r="D19">
-        <v>16.41364916036618</v>
+        <v>16.43740832900579</v>
       </c>
       <c r="E19">
-        <v>4.165</v>
+        <v>4.41</v>
       </c>
       <c r="F19">
-        <v>4.165</v>
+        <v>4.41</v>
       </c>
       <c r="G19">
         <v>8.48</v>
@@ -2949,28 +2949,28 @@
         <v>4.15</v>
       </c>
       <c r="M19">
-        <v>0.2094995</v>
+        <v>0.221823</v>
       </c>
       <c r="N19">
-        <v>3.9405005</v>
+        <v>3.928177</v>
       </c>
       <c r="O19">
-        <v>0.9063151150000001</v>
+        <v>0.9034807100000001</v>
       </c>
       <c r="P19">
-        <v>3.034185385</v>
+        <v>3.02469629</v>
       </c>
       <c r="Q19">
-        <v>3.804185385</v>
+        <v>3.79469629</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1391150328275249</v>
+        <v>0.1400269392881499</v>
       </c>
       <c r="T19">
-        <v>1.443553880105091</v>
+        <v>1.457660783029952</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.80911648953816</v>
+        <v>18.70861001789715</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2995,22 +2995,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1217936702162829</v>
+        <v>0.1215375931857202</v>
       </c>
       <c r="C20">
-        <v>20.50740832900578</v>
+        <v>20.28623638134072</v>
       </c>
       <c r="D20">
-        <v>16.43740832900578</v>
+        <v>16.46123638134073</v>
       </c>
       <c r="E20">
-        <v>4.41</v>
+        <v>4.655</v>
       </c>
       <c r="F20">
-        <v>4.41</v>
+        <v>4.655</v>
       </c>
       <c r="G20">
         <v>8.48</v>
@@ -3031,28 +3031,28 @@
         <v>4.15</v>
       </c>
       <c r="M20">
-        <v>0.221823</v>
+        <v>0.2341465</v>
       </c>
       <c r="N20">
-        <v>3.928177</v>
+        <v>3.9158535</v>
       </c>
       <c r="O20">
-        <v>0.9034807100000001</v>
+        <v>0.9006463050000001</v>
       </c>
       <c r="P20">
-        <v>3.02469629</v>
+        <v>3.015207195</v>
       </c>
       <c r="Q20">
-        <v>3.79469629</v>
+        <v>3.785207195</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1400269392881499</v>
+        <v>0.1409613619576792</v>
       </c>
       <c r="T20">
-        <v>1.457660783029952</v>
+        <v>1.472116004545551</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.70861001789715</v>
+        <v>17.72394633274467</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3077,22 +3077,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1215375931857202</v>
+        <v>0.1212815161551574</v>
       </c>
       <c r="C21">
-        <v>20.28623638134072</v>
+        <v>20.06513361737216</v>
       </c>
       <c r="D21">
-        <v>16.46123638134073</v>
+        <v>16.48513361737216</v>
       </c>
       <c r="E21">
-        <v>4.655</v>
+        <v>4.9</v>
       </c>
       <c r="F21">
-        <v>4.655</v>
+        <v>4.9</v>
       </c>
       <c r="G21">
         <v>8.48</v>
@@ -3113,28 +3113,28 @@
         <v>4.15</v>
       </c>
       <c r="M21">
-        <v>0.2341465</v>
+        <v>0.24647</v>
       </c>
       <c r="N21">
-        <v>3.9158535</v>
+        <v>3.90353</v>
       </c>
       <c r="O21">
-        <v>0.9006463050000001</v>
+        <v>0.8978119000000001</v>
       </c>
       <c r="P21">
-        <v>3.015207195</v>
+        <v>3.0057181</v>
       </c>
       <c r="Q21">
-        <v>3.785207195</v>
+        <v>3.7757181</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1409613619576792</v>
+        <v>0.1419191451939467</v>
       </c>
       <c r="T21">
-        <v>1.472116004545551</v>
+        <v>1.486932606599039</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.72394633274467</v>
+        <v>16.83774901610744</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3159,22 +3159,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1212815161551574</v>
+        <v>0.1210254391245947</v>
       </c>
       <c r="C22">
-        <v>20.06513361737216</v>
+        <v>19.84410033884584</v>
       </c>
       <c r="D22">
-        <v>16.48513361737216</v>
+        <v>16.50910033884584</v>
       </c>
       <c r="E22">
-        <v>4.9</v>
+        <v>5.145</v>
       </c>
       <c r="F22">
-        <v>4.9</v>
+        <v>5.145</v>
       </c>
       <c r="G22">
         <v>8.48</v>
@@ -3195,28 +3195,28 @@
         <v>4.15</v>
       </c>
       <c r="M22">
-        <v>0.24647</v>
+        <v>0.2587935</v>
       </c>
       <c r="N22">
-        <v>3.90353</v>
+        <v>3.8912065</v>
       </c>
       <c r="O22">
-        <v>0.8978119000000001</v>
+        <v>0.8949774950000001</v>
       </c>
       <c r="P22">
-        <v>3.0057181</v>
+        <v>2.996229005</v>
       </c>
       <c r="Q22">
-        <v>3.7757181</v>
+        <v>3.766229005</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1419191451939467</v>
+        <v>0.1429011761070819</v>
       </c>
       <c r="T22">
-        <v>1.486932606599039</v>
+        <v>1.502124312501983</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.83774901610744</v>
+        <v>16.03595144391185</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3241,22 +3241,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1210254391245947</v>
+        <v>0.1207693620940319</v>
       </c>
       <c r="C23">
-        <v>19.84410033884584</v>
+        <v>19.62313684926484</v>
       </c>
       <c r="D23">
-        <v>16.50910033884584</v>
+        <v>16.53313684926484</v>
       </c>
       <c r="E23">
-        <v>5.145</v>
+        <v>5.39</v>
       </c>
       <c r="F23">
-        <v>5.145</v>
+        <v>5.39</v>
       </c>
       <c r="G23">
         <v>8.48</v>
@@ -3277,28 +3277,28 @@
         <v>4.15</v>
       </c>
       <c r="M23">
-        <v>0.2587935</v>
+        <v>0.271117</v>
       </c>
       <c r="N23">
-        <v>3.8912065</v>
+        <v>3.878883000000001</v>
       </c>
       <c r="O23">
-        <v>0.8949774950000001</v>
+        <v>0.8921430900000001</v>
       </c>
       <c r="P23">
-        <v>2.996229005</v>
+        <v>2.98673991</v>
       </c>
       <c r="Q23">
-        <v>3.766229005</v>
+        <v>3.75673991</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1429011761070819</v>
+        <v>0.1439083873000409</v>
       </c>
       <c r="T23">
-        <v>1.502124312501983</v>
+        <v>1.517705549325515</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.03595144391185</v>
+        <v>15.30704456009767</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3323,22 +3323,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1207693620940319</v>
+        <v>0.1205132850634692</v>
       </c>
       <c r="C24">
-        <v>19.62313684926484</v>
+        <v>19.40224345390236</v>
       </c>
       <c r="D24">
-        <v>16.53313684926484</v>
+        <v>16.55724345390236</v>
       </c>
       <c r="E24">
-        <v>5.39</v>
+        <v>5.635000000000001</v>
       </c>
       <c r="F24">
-        <v>5.39</v>
+        <v>5.635000000000001</v>
       </c>
       <c r="G24">
         <v>8.48</v>
@@ -3359,28 +3359,28 @@
         <v>4.15</v>
       </c>
       <c r="M24">
-        <v>0.271117</v>
+        <v>0.2834405</v>
       </c>
       <c r="N24">
-        <v>3.878883000000001</v>
+        <v>3.8665595</v>
       </c>
       <c r="O24">
-        <v>0.8921430900000001</v>
+        <v>0.889308685</v>
       </c>
       <c r="P24">
-        <v>2.98673991</v>
+        <v>2.977250815</v>
       </c>
       <c r="Q24">
-        <v>3.75673991</v>
+        <v>3.747250815</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1439083873000409</v>
+        <v>0.1449417598226872</v>
       </c>
       <c r="T24">
-        <v>1.517705549325515</v>
+        <v>1.533691493599009</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.30704456009767</v>
+        <v>14.64152088357168</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3405,22 +3405,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1205132850634692</v>
+        <v>0.1202572080329064</v>
       </c>
       <c r="C25">
-        <v>19.40224345390236</v>
+        <v>19.18142045981464</v>
       </c>
       <c r="D25">
-        <v>16.55724345390236</v>
+        <v>16.58142045981464</v>
       </c>
       <c r="E25">
-        <v>5.635000000000001</v>
+        <v>5.880000000000001</v>
       </c>
       <c r="F25">
-        <v>5.635000000000001</v>
+        <v>5.880000000000001</v>
       </c>
       <c r="G25">
         <v>8.48</v>
@@ -3441,28 +3441,28 @@
         <v>4.15</v>
       </c>
       <c r="M25">
-        <v>0.2834405</v>
+        <v>0.295764</v>
       </c>
       <c r="N25">
-        <v>3.8665595</v>
+        <v>3.854236</v>
       </c>
       <c r="O25">
-        <v>0.889308685</v>
+        <v>0.8864742800000001</v>
       </c>
       <c r="P25">
-        <v>2.977250815</v>
+        <v>2.96776172</v>
       </c>
       <c r="Q25">
-        <v>3.747250815</v>
+        <v>3.73776172</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1449417598226872</v>
+        <v>0.1460023263590874</v>
       </c>
       <c r="T25">
-        <v>1.533691493599009</v>
+        <v>1.550098120616542</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.64152088357168</v>
+        <v>14.03145751342286</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3487,22 +3487,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1202572080329064</v>
+        <v>0.1200011310023437</v>
       </c>
       <c r="C26">
-        <v>19.18142045981464</v>
+        <v>18.96066817585401</v>
       </c>
       <c r="D26">
-        <v>16.58142045981464</v>
+        <v>16.60566817585401</v>
       </c>
       <c r="E26">
-        <v>5.88</v>
+        <v>6.125</v>
       </c>
       <c r="F26">
-        <v>5.88</v>
+        <v>6.125</v>
       </c>
       <c r="G26">
         <v>8.48</v>
@@ -3523,28 +3523,28 @@
         <v>4.15</v>
       </c>
       <c r="M26">
-        <v>0.295764</v>
+        <v>0.3080875</v>
       </c>
       <c r="N26">
-        <v>3.854236</v>
+        <v>3.8419125</v>
       </c>
       <c r="O26">
-        <v>0.8864742800000001</v>
+        <v>0.8836398750000001</v>
       </c>
       <c r="P26">
-        <v>2.96776172</v>
+        <v>2.958272625</v>
       </c>
       <c r="Q26">
-        <v>3.73776172</v>
+        <v>3.728272625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1460023263590874</v>
+        <v>0.1470911746697915</v>
       </c>
       <c r="T26">
-        <v>1.550098120616542</v>
+        <v>1.566942257687876</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.03145751342287</v>
+        <v>13.47019921288595</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3569,22 +3569,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1200011310023437</v>
+        <v>0.1197450539717809</v>
       </c>
       <c r="C27">
-        <v>18.96066817585401</v>
+        <v>18.73998691268204</v>
       </c>
       <c r="D27">
-        <v>16.60566817585401</v>
+        <v>16.62998691268204</v>
       </c>
       <c r="E27">
-        <v>6.125</v>
+        <v>6.37</v>
       </c>
       <c r="F27">
-        <v>6.125</v>
+        <v>6.37</v>
       </c>
       <c r="G27">
         <v>8.48</v>
@@ -3605,28 +3605,28 @@
         <v>4.15</v>
       </c>
       <c r="M27">
-        <v>0.3080875</v>
+        <v>0.320411</v>
       </c>
       <c r="N27">
-        <v>3.8419125</v>
+        <v>3.829589</v>
       </c>
       <c r="O27">
-        <v>0.8836398750000001</v>
+        <v>0.8808054700000001</v>
       </c>
       <c r="P27">
-        <v>2.958272625</v>
+        <v>2.94878353</v>
       </c>
       <c r="Q27">
-        <v>3.728272625</v>
+        <v>3.71878353</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1470911746697915</v>
+        <v>0.1482094513132175</v>
       </c>
       <c r="T27">
-        <v>1.566942257687876</v>
+        <v>1.584241641707085</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.47019921288595</v>
+        <v>12.95211462777495</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3651,22 +3651,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1197450539717809</v>
+        <v>0.1198008269412182</v>
       </c>
       <c r="C28">
-        <v>18.73998691268204</v>
+        <v>18.48968428412344</v>
       </c>
       <c r="D28">
-        <v>16.62998691268204</v>
+        <v>16.62468428412344</v>
       </c>
       <c r="E28">
-        <v>6.37</v>
+        <v>6.615</v>
       </c>
       <c r="F28">
-        <v>6.37</v>
+        <v>6.615</v>
       </c>
       <c r="G28">
         <v>8.48</v>
@@ -3687,45 +3687,45 @@
         <v>4.15</v>
       </c>
       <c r="M28">
-        <v>0.320411</v>
+        <v>0.342657</v>
       </c>
       <c r="N28">
-        <v>3.829589</v>
+        <v>3.807343</v>
       </c>
       <c r="O28">
-        <v>0.8808054700000001</v>
+        <v>0.8756888900000002</v>
       </c>
       <c r="P28">
-        <v>2.94878353</v>
+        <v>2.93165411</v>
       </c>
       <c r="Q28">
-        <v>3.71878353</v>
+        <v>3.70165411</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1482094513132175</v>
+        <v>0.1493583656729016</v>
       </c>
       <c r="T28">
-        <v>1.584241641707085</v>
+        <v>1.602014981452846</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.23</v>
       </c>
       <c r="W28">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>12.95211462777495</v>
+        <v>12.11123660103252</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3733,22 +3733,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1198008269412182</v>
+        <v>0.1195562999106554</v>
       </c>
       <c r="C29">
-        <v>18.48968428412344</v>
+        <v>18.26795787382393</v>
       </c>
       <c r="D29">
-        <v>16.62468428412344</v>
+        <v>16.64795787382393</v>
       </c>
       <c r="E29">
-        <v>6.615</v>
+        <v>6.86</v>
       </c>
       <c r="F29">
-        <v>6.615</v>
+        <v>6.86</v>
       </c>
       <c r="G29">
         <v>8.48</v>
@@ -3769,28 +3769,28 @@
         <v>4.15</v>
       </c>
       <c r="M29">
-        <v>0.342657</v>
+        <v>0.355348</v>
       </c>
       <c r="N29">
-        <v>3.807343</v>
+        <v>3.794652</v>
       </c>
       <c r="O29">
-        <v>0.8756888900000002</v>
+        <v>0.8727699600000001</v>
       </c>
       <c r="P29">
-        <v>2.93165411</v>
+        <v>2.92188204</v>
       </c>
       <c r="Q29">
-        <v>3.70165411</v>
+        <v>3.691882039999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1493583656729016</v>
+        <v>0.1505391943203548</v>
       </c>
       <c r="T29">
-        <v>1.602014981452846</v>
+        <v>1.620282025080435</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.11123660103252</v>
+        <v>11.67869243670993</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1195562999106554</v>
+        <v>0.1193117728800927</v>
       </c>
       <c r="C30">
-        <v>18.26795787382393</v>
+        <v>18.04629671821723</v>
       </c>
       <c r="D30">
-        <v>16.64795787382393</v>
+        <v>16.67129671821723</v>
       </c>
       <c r="E30">
-        <v>6.86</v>
+        <v>7.105</v>
       </c>
       <c r="F30">
-        <v>6.86</v>
+        <v>7.105</v>
       </c>
       <c r="G30">
         <v>8.48</v>
@@ -3851,28 +3851,28 @@
         <v>4.15</v>
       </c>
       <c r="M30">
-        <v>0.355348</v>
+        <v>0.368039</v>
       </c>
       <c r="N30">
-        <v>3.794652</v>
+        <v>3.781961</v>
       </c>
       <c r="O30">
-        <v>0.8727699600000001</v>
+        <v>0.8698510300000001</v>
       </c>
       <c r="P30">
-        <v>2.92188204</v>
+        <v>2.91210997</v>
       </c>
       <c r="Q30">
-        <v>3.691882039999999</v>
+        <v>3.68210997</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1505391943203548</v>
+        <v>0.1517532857466094</v>
       </c>
       <c r="T30">
-        <v>1.620282025080435</v>
+        <v>1.639063633317251</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.67869243670993</v>
+        <v>11.27597890440959</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3897,22 +3897,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1193117728800927</v>
+        <v>0.1190672458495299</v>
       </c>
       <c r="C31">
-        <v>18.04629671821723</v>
+        <v>17.82470109213114</v>
       </c>
       <c r="D31">
-        <v>16.67129671821723</v>
+        <v>16.69470109213114</v>
       </c>
       <c r="E31">
-        <v>7.105</v>
+        <v>7.35</v>
       </c>
       <c r="F31">
-        <v>7.105</v>
+        <v>7.35</v>
       </c>
       <c r="G31">
         <v>8.48</v>
@@ -3933,28 +3933,28 @@
         <v>4.15</v>
       </c>
       <c r="M31">
-        <v>0.3680389999999999</v>
+        <v>0.38073</v>
       </c>
       <c r="N31">
-        <v>3.781961</v>
+        <v>3.769270000000001</v>
       </c>
       <c r="O31">
-        <v>0.8698510300000001</v>
+        <v>0.8669321000000002</v>
       </c>
       <c r="P31">
-        <v>2.91210997</v>
+        <v>2.9023379</v>
       </c>
       <c r="Q31">
-        <v>3.68210997</v>
+        <v>3.6723379</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1517532857466094</v>
+        <v>0.1530020654993285</v>
       </c>
       <c r="T31">
-        <v>1.639063633317251</v>
+        <v>1.658381858932262</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.27597890440959</v>
+        <v>10.90011294092927</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1190672458495299</v>
+        <v>0.1188227188189672</v>
       </c>
       <c r="C32">
-        <v>17.82470109213114</v>
+        <v>17.60317127193891</v>
       </c>
       <c r="D32">
-        <v>16.69470109213114</v>
+        <v>16.71817127193891</v>
       </c>
       <c r="E32">
-        <v>7.35</v>
+        <v>7.595</v>
       </c>
       <c r="F32">
-        <v>7.35</v>
+        <v>7.595</v>
       </c>
       <c r="G32">
         <v>8.48</v>
@@ -4015,28 +4015,28 @@
         <v>4.15</v>
       </c>
       <c r="M32">
-        <v>0.38073</v>
+        <v>0.393421</v>
       </c>
       <c r="N32">
-        <v>3.769270000000001</v>
+        <v>3.756579</v>
       </c>
       <c r="O32">
-        <v>0.8669321000000002</v>
+        <v>0.8640131700000001</v>
       </c>
       <c r="P32">
-        <v>2.9023379</v>
+        <v>2.89256583</v>
       </c>
       <c r="Q32">
-        <v>3.6723379</v>
+        <v>3.66256583</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1530020654993285</v>
+        <v>0.1542870417666191</v>
       </c>
       <c r="T32">
-        <v>1.658381858932262</v>
+        <v>1.678260033115824</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.90011294092927</v>
+        <v>10.54849639444768</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1188227188189672</v>
+        <v>0.1185781917884044</v>
       </c>
       <c r="C33">
-        <v>17.60317127193891</v>
+        <v>17.38170753557013</v>
       </c>
       <c r="D33">
-        <v>16.71817127193891</v>
+        <v>16.74170753557013</v>
       </c>
       <c r="E33">
-        <v>7.595</v>
+        <v>7.84</v>
       </c>
       <c r="F33">
-        <v>7.595</v>
+        <v>7.84</v>
       </c>
       <c r="G33">
         <v>8.48</v>
@@ -4097,28 +4097,28 @@
         <v>4.15</v>
       </c>
       <c r="M33">
-        <v>0.393421</v>
+        <v>0.406112</v>
       </c>
       <c r="N33">
-        <v>3.756579</v>
+        <v>3.743888000000001</v>
       </c>
       <c r="O33">
-        <v>0.8640131700000001</v>
+        <v>0.8610942400000001</v>
       </c>
       <c r="P33">
-        <v>2.89256583</v>
+        <v>2.88279376</v>
       </c>
       <c r="Q33">
-        <v>3.66256583</v>
+        <v>3.65279376</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1542870417666191</v>
+        <v>0.1556098114535359</v>
       </c>
       <c r="T33">
-        <v>1.678260033115824</v>
+        <v>1.698722859481255</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.54849639444768</v>
+        <v>10.21885588212119</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4143,22 +4143,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1185781917884044</v>
+        <v>0.1183336647578417</v>
       </c>
       <c r="C34">
-        <v>17.38170753557013</v>
+        <v>17.16031016252172</v>
       </c>
       <c r="D34">
-        <v>16.74170753557013</v>
+        <v>16.76531016252172</v>
       </c>
       <c r="E34">
-        <v>7.84</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="F34">
-        <v>7.84</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="G34">
         <v>8.48</v>
@@ -4179,28 +4179,28 @@
         <v>4.15</v>
       </c>
       <c r="M34">
-        <v>0.406112</v>
+        <v>0.418803</v>
       </c>
       <c r="N34">
-        <v>3.743888000000001</v>
+        <v>3.731197</v>
       </c>
       <c r="O34">
-        <v>0.8610942400000001</v>
+        <v>0.8581753100000001</v>
       </c>
       <c r="P34">
-        <v>2.88279376</v>
+        <v>2.87302169</v>
       </c>
       <c r="Q34">
-        <v>3.65279376</v>
+        <v>3.64302169</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1556098114535359</v>
+        <v>0.1569720668027488</v>
       </c>
       <c r="T34">
-        <v>1.698722859481255</v>
+        <v>1.719796516484461</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.21885588212119</v>
+        <v>9.90919358266297</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4225,22 +4225,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1183336647578417</v>
+        <v>0.1185341977272789</v>
       </c>
       <c r="C35">
-        <v>17.16031016252172</v>
+        <v>16.89594909636779</v>
       </c>
       <c r="D35">
-        <v>16.76531016252172</v>
+        <v>16.7459490963678</v>
       </c>
       <c r="E35">
-        <v>8.085000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="F35">
-        <v>8.085000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="G35">
         <v>8.48</v>
@@ -4261,45 +4261,45 @@
         <v>4.15</v>
       </c>
       <c r="M35">
-        <v>0.418803</v>
+        <v>0.445655</v>
       </c>
       <c r="N35">
-        <v>3.731197</v>
+        <v>3.704345</v>
       </c>
       <c r="O35">
-        <v>0.8581753100000001</v>
+        <v>0.8519993500000002</v>
       </c>
       <c r="P35">
-        <v>2.87302169</v>
+        <v>2.85234565</v>
       </c>
       <c r="Q35">
-        <v>3.64302169</v>
+        <v>3.62234565</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1569720668027488</v>
+        <v>0.1583756026170893</v>
       </c>
       <c r="T35">
-        <v>1.719796516484461</v>
+        <v>1.74150876915443</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.23</v>
       </c>
       <c r="W35">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>9.90919358266297</v>
+        <v>9.312136069381024</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4307,22 +4307,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1185341977272789</v>
+        <v>0.1183027606967162</v>
       </c>
       <c r="C36">
-        <v>16.89594909636779</v>
+        <v>16.67329787122136</v>
       </c>
       <c r="D36">
-        <v>16.7459490963678</v>
+        <v>16.76829787122136</v>
       </c>
       <c r="E36">
-        <v>8.33</v>
+        <v>8.575000000000001</v>
       </c>
       <c r="F36">
-        <v>8.33</v>
+        <v>8.575000000000001</v>
       </c>
       <c r="G36">
         <v>8.48</v>
@@ -4343,28 +4343,28 @@
         <v>4.15</v>
       </c>
       <c r="M36">
-        <v>0.445655</v>
+        <v>0.4587625000000001</v>
       </c>
       <c r="N36">
-        <v>3.704345</v>
+        <v>3.6912375</v>
       </c>
       <c r="O36">
-        <v>0.8519993500000002</v>
+        <v>0.848984625</v>
       </c>
       <c r="P36">
-        <v>2.85234565</v>
+        <v>2.842252875</v>
       </c>
       <c r="Q36">
-        <v>3.62234565</v>
+        <v>3.612252875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1583756026170893</v>
+        <v>0.1598223241487941</v>
       </c>
       <c r="T36">
-        <v>1.74150876915443</v>
+        <v>1.763889091137322</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.312136069381024</v>
+        <v>9.046075038827279</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4389,22 +4389,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1183027606967162</v>
+        <v>0.1180713236661534</v>
       </c>
       <c r="C37">
-        <v>16.67329787122136</v>
+        <v>16.45070637815747</v>
       </c>
       <c r="D37">
-        <v>16.76829787122136</v>
+        <v>16.79070637815747</v>
       </c>
       <c r="E37">
-        <v>8.575000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="F37">
-        <v>8.575000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G37">
         <v>8.48</v>
@@ -4425,28 +4425,28 @@
         <v>4.15</v>
       </c>
       <c r="M37">
-        <v>0.4587625000000001</v>
+        <v>0.47187</v>
       </c>
       <c r="N37">
-        <v>3.6912375</v>
+        <v>3.67813</v>
       </c>
       <c r="O37">
-        <v>0.848984625</v>
+        <v>0.8459699000000002</v>
       </c>
       <c r="P37">
-        <v>2.842252875</v>
+        <v>2.8321601</v>
       </c>
       <c r="Q37">
-        <v>3.612252875</v>
+        <v>3.6021601</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1598223241487941</v>
+        <v>0.1613142557283647</v>
       </c>
       <c r="T37">
-        <v>1.763889091137322</v>
+        <v>1.786968798182179</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.046075038827279</v>
+        <v>8.794795176637635</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4471,22 +4471,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1180713236661534</v>
+        <v>0.1178398866355907</v>
       </c>
       <c r="C38">
-        <v>16.45070637815747</v>
+        <v>16.22817485696753</v>
       </c>
       <c r="D38">
-        <v>16.79070637815747</v>
+        <v>16.81317485696754</v>
       </c>
       <c r="E38">
-        <v>8.82</v>
+        <v>9.065</v>
       </c>
       <c r="F38">
-        <v>8.82</v>
+        <v>9.065</v>
       </c>
       <c r="G38">
         <v>8.48</v>
@@ -4507,28 +4507,28 @@
         <v>4.15</v>
       </c>
       <c r="M38">
-        <v>0.47187</v>
+        <v>0.4849775</v>
       </c>
       <c r="N38">
-        <v>3.67813</v>
+        <v>3.665022500000001</v>
       </c>
       <c r="O38">
-        <v>0.8459699000000002</v>
+        <v>0.8429551750000002</v>
       </c>
       <c r="P38">
-        <v>2.8321601</v>
+        <v>2.822067325</v>
       </c>
       <c r="Q38">
-        <v>3.6021601</v>
+        <v>3.592067325</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1613142557283647</v>
+        <v>0.1628535502152233</v>
       </c>
       <c r="T38">
-        <v>1.786968798182179</v>
+        <v>1.810781194339571</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.794795176637635</v>
+        <v>8.557098009701484</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4553,22 +4553,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1178398866355907</v>
+        <v>0.1176084496050279</v>
       </c>
       <c r="C39">
-        <v>16.22817485696753</v>
+        <v>16.00570354872819</v>
       </c>
       <c r="D39">
-        <v>16.81317485696754</v>
+        <v>16.83570354872819</v>
       </c>
       <c r="E39">
-        <v>9.065</v>
+        <v>9.31</v>
       </c>
       <c r="F39">
-        <v>9.065</v>
+        <v>9.31</v>
       </c>
       <c r="G39">
         <v>8.48</v>
@@ -4589,28 +4589,28 @@
         <v>4.15</v>
       </c>
       <c r="M39">
-        <v>0.4849775</v>
+        <v>0.498085</v>
       </c>
       <c r="N39">
-        <v>3.665022500000001</v>
+        <v>3.651915</v>
       </c>
       <c r="O39">
-        <v>0.8429551750000002</v>
+        <v>0.8399404500000001</v>
       </c>
       <c r="P39">
-        <v>2.822067325</v>
+        <v>2.81197455</v>
       </c>
       <c r="Q39">
-        <v>3.592067325</v>
+        <v>3.58197455</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1628535502152233</v>
+        <v>0.1644424993629483</v>
       </c>
       <c r="T39">
-        <v>1.810781194339571</v>
+        <v>1.835361732308492</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.557098009701484</v>
+        <v>8.331911219972495</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4635,22 +4635,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1176084496050279</v>
+        <v>0.1173770125744652</v>
       </c>
       <c r="C40">
-        <v>16.00570354872819</v>
+        <v>15.78329269580992</v>
       </c>
       <c r="D40">
-        <v>16.83570354872819</v>
+        <v>16.85829269580992</v>
       </c>
       <c r="E40">
-        <v>9.31</v>
+        <v>9.555</v>
       </c>
       <c r="F40">
-        <v>9.31</v>
+        <v>9.555</v>
       </c>
       <c r="G40">
         <v>8.48</v>
@@ -4671,28 +4671,28 @@
         <v>4.15</v>
       </c>
       <c r="M40">
-        <v>0.498085</v>
+        <v>0.5111924999999999</v>
       </c>
       <c r="N40">
-        <v>3.651915</v>
+        <v>3.6388075</v>
       </c>
       <c r="O40">
-        <v>0.8399404500000001</v>
+        <v>0.8369257250000002</v>
       </c>
       <c r="P40">
-        <v>2.81197455</v>
+        <v>2.801881775</v>
       </c>
       <c r="Q40">
-        <v>3.58197455</v>
+        <v>3.571881775</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1644424993629483</v>
+        <v>0.1660835452040413</v>
       </c>
       <c r="T40">
-        <v>1.835361732308492</v>
+        <v>1.860748189555082</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.331911219972495</v>
+        <v>8.118272470742433</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1173770125744652</v>
+        <v>0.1171455755439024</v>
       </c>
       <c r="C41">
-        <v>15.78329269580992</v>
+        <v>15.56094254188573</v>
       </c>
       <c r="D41">
-        <v>16.85829269580992</v>
+        <v>16.88094254188573</v>
       </c>
       <c r="E41">
-        <v>9.555</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F41">
-        <v>9.555</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G41">
         <v>8.48</v>
@@ -4753,28 +4753,28 @@
         <v>4.15</v>
       </c>
       <c r="M41">
-        <v>0.5111924999999999</v>
+        <v>0.5243</v>
       </c>
       <c r="N41">
-        <v>3.6388075</v>
+        <v>3.6257</v>
       </c>
       <c r="O41">
-        <v>0.8369257250000002</v>
+        <v>0.8339110000000001</v>
       </c>
       <c r="P41">
-        <v>2.801881775</v>
+        <v>2.791789</v>
       </c>
       <c r="Q41">
-        <v>3.571881775</v>
+        <v>3.561789</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1660835452040413</v>
+        <v>0.1677792925731707</v>
       </c>
       <c r="T41">
-        <v>1.860748189555082</v>
+        <v>1.886980862043225</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.118272470742433</v>
+        <v>7.915315658973871</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4799,22 +4799,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1171455755439024</v>
+        <v>0.1169141385133397</v>
       </c>
       <c r="C42">
-        <v>15.56094254188573</v>
+        <v>15.33865333193997</v>
       </c>
       <c r="D42">
-        <v>16.88094254188573</v>
+        <v>16.90365333193997</v>
       </c>
       <c r="E42">
-        <v>9.800000000000001</v>
+        <v>10.045</v>
       </c>
       <c r="F42">
-        <v>9.800000000000001</v>
+        <v>10.045</v>
       </c>
       <c r="G42">
         <v>8.48</v>
@@ -4835,28 +4835,28 @@
         <v>4.15</v>
       </c>
       <c r="M42">
-        <v>0.5243</v>
+        <v>0.5374075</v>
       </c>
       <c r="N42">
-        <v>3.6257</v>
+        <v>3.6125925</v>
       </c>
       <c r="O42">
-        <v>0.8339110000000001</v>
+        <v>0.8308962750000001</v>
       </c>
       <c r="P42">
-        <v>2.791789</v>
+        <v>2.781696225</v>
       </c>
       <c r="Q42">
-        <v>3.561789</v>
+        <v>3.551696225</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1677792925731707</v>
+        <v>0.1695325229039656</v>
       </c>
       <c r="T42">
-        <v>1.886980862043225</v>
+        <v>1.91410277766656</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.915315658973871</v>
+        <v>7.722259179486702</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4881,22 +4881,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1169141385133397</v>
+        <v>0.1169414214827769</v>
       </c>
       <c r="C43">
-        <v>15.33865333193997</v>
+        <v>15.09097289222485</v>
       </c>
       <c r="D43">
-        <v>16.90365333193997</v>
+        <v>16.90097289222485</v>
       </c>
       <c r="E43">
-        <v>10.045</v>
+        <v>10.29</v>
       </c>
       <c r="F43">
-        <v>10.045</v>
+        <v>10.29</v>
       </c>
       <c r="G43">
         <v>8.48</v>
@@ -4917,45 +4917,45 @@
         <v>4.15</v>
       </c>
       <c r="M43">
-        <v>0.5374075</v>
+        <v>0.5587470000000001</v>
       </c>
       <c r="N43">
-        <v>3.6125925</v>
+        <v>3.591253</v>
       </c>
       <c r="O43">
-        <v>0.8308962750000001</v>
+        <v>0.82598819</v>
       </c>
       <c r="P43">
-        <v>2.781696225</v>
+        <v>2.76526481</v>
       </c>
       <c r="Q43">
-        <v>3.551696225</v>
+        <v>3.53526481</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1695325229039656</v>
+        <v>0.1713462094530637</v>
       </c>
       <c r="T43">
-        <v>1.91410277766656</v>
+        <v>1.942159931759665</v>
       </c>
       <c r="U43">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.23</v>
       </c>
       <c r="W43">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>7.722259179486702</v>
+        <v>7.427332943174638</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.116941421482777</v>
+        <v>0.1167161444522142</v>
       </c>
       <c r="C44">
-        <v>15.09097289222484</v>
+        <v>14.86813093813184</v>
       </c>
       <c r="D44">
-        <v>16.90097289222484</v>
+        <v>16.92313093813184</v>
       </c>
       <c r="E44">
-        <v>10.29</v>
+        <v>10.535</v>
       </c>
       <c r="F44">
-        <v>10.29</v>
+        <v>10.535</v>
       </c>
       <c r="G44">
         <v>8.48</v>
@@ -4999,28 +4999,28 @@
         <v>4.15</v>
       </c>
       <c r="M44">
-        <v>0.558747</v>
+        <v>0.5720505</v>
       </c>
       <c r="N44">
-        <v>3.591253</v>
+        <v>3.5779495</v>
       </c>
       <c r="O44">
-        <v>0.8259881900000001</v>
+        <v>0.8229283850000001</v>
       </c>
       <c r="P44">
-        <v>2.765264810000001</v>
+        <v>2.755021115</v>
       </c>
       <c r="Q44">
-        <v>3.53526481</v>
+        <v>3.525021115</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1713462094530637</v>
+        <v>0.1732235341266916</v>
       </c>
       <c r="T44">
-        <v>1.942159931759665</v>
+        <v>1.971201547399896</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.42733294317464</v>
+        <v>7.254604270077555</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1167161444522142</v>
+        <v>0.1164908674216515</v>
       </c>
       <c r="C45">
-        <v>14.86813093813184</v>
+        <v>14.64534716099059</v>
       </c>
       <c r="D45">
-        <v>16.92313093813184</v>
+        <v>16.94534716099059</v>
       </c>
       <c r="E45">
-        <v>10.535</v>
+        <v>10.78</v>
       </c>
       <c r="F45">
-        <v>10.535</v>
+        <v>10.78</v>
       </c>
       <c r="G45">
         <v>8.48</v>
@@ -5081,28 +5081,28 @@
         <v>4.15</v>
       </c>
       <c r="M45">
-        <v>0.5720505</v>
+        <v>0.5853539999999999</v>
       </c>
       <c r="N45">
-        <v>3.5779495</v>
+        <v>3.564646000000001</v>
       </c>
       <c r="O45">
-        <v>0.8229283850000001</v>
+        <v>0.8198685800000002</v>
       </c>
       <c r="P45">
-        <v>2.755021115</v>
+        <v>2.744777420000001</v>
       </c>
       <c r="Q45">
-        <v>3.525021115</v>
+        <v>3.51477742</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1732235341266916</v>
+        <v>0.1751679061100919</v>
       </c>
       <c r="T45">
-        <v>1.971201547399896</v>
+        <v>2.001280363598707</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.254604270077555</v>
+        <v>7.089726900303067</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1164908674216515</v>
+        <v>0.1162655903910887</v>
       </c>
       <c r="C46">
-        <v>14.64534716099059</v>
+        <v>14.42262179022159</v>
       </c>
       <c r="D46">
-        <v>16.94534716099059</v>
+        <v>16.96762179022159</v>
       </c>
       <c r="E46">
-        <v>10.78</v>
+        <v>11.025</v>
       </c>
       <c r="F46">
-        <v>10.78</v>
+        <v>11.025</v>
       </c>
       <c r="G46">
         <v>8.48</v>
@@ -5163,28 +5163,28 @@
         <v>4.15</v>
       </c>
       <c r="M46">
-        <v>0.5853539999999999</v>
+        <v>0.5986575000000001</v>
       </c>
       <c r="N46">
-        <v>3.564646000000001</v>
+        <v>3.551342500000001</v>
       </c>
       <c r="O46">
-        <v>0.8198685800000002</v>
+        <v>0.8168087750000002</v>
       </c>
       <c r="P46">
-        <v>2.744777420000001</v>
+        <v>2.734533725</v>
       </c>
       <c r="Q46">
-        <v>3.51477742</v>
+        <v>3.504533725</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1751679061100919</v>
+        <v>0.1771829825292522</v>
       </c>
       <c r="T46">
-        <v>2.001280363598707</v>
+        <v>2.03245295493202</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.089726900303067</v>
+        <v>6.932177413629663</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5209,22 +5209,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1162655903910887</v>
+        <v>0.116040313360526</v>
       </c>
       <c r="C47">
-        <v>14.42262179022159</v>
+        <v>14.19995505645321</v>
       </c>
       <c r="D47">
-        <v>16.96762179022159</v>
+        <v>16.98995505645321</v>
       </c>
       <c r="E47">
-        <v>11.025</v>
+        <v>11.27</v>
       </c>
       <c r="F47">
-        <v>11.025</v>
+        <v>11.27</v>
       </c>
       <c r="G47">
         <v>8.48</v>
@@ -5245,28 +5245,28 @@
         <v>4.15</v>
       </c>
       <c r="M47">
-        <v>0.5986575000000001</v>
+        <v>0.6119610000000001</v>
       </c>
       <c r="N47">
-        <v>3.551342500000001</v>
+        <v>3.538039</v>
       </c>
       <c r="O47">
-        <v>0.8168087750000002</v>
+        <v>0.8137489700000001</v>
       </c>
       <c r="P47">
-        <v>2.734533725</v>
+        <v>2.72429003</v>
       </c>
       <c r="Q47">
-        <v>3.504533725</v>
+        <v>3.49429003</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1771829825292522</v>
+        <v>0.1792726914083814</v>
       </c>
       <c r="T47">
-        <v>2.03245295493202</v>
+        <v>2.064780086685086</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.932177413629663</v>
+        <v>6.781477904637714</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5291,22 +5291,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.116040313360526</v>
+        <v>0.1158150363299632</v>
       </c>
       <c r="C48">
-        <v>14.19995505645321</v>
+        <v>13.9773471915297</v>
       </c>
       <c r="D48">
-        <v>16.98995505645321</v>
+        <v>17.0123471915297</v>
       </c>
       <c r="E48">
-        <v>11.27</v>
+        <v>11.515</v>
       </c>
       <c r="F48">
-        <v>11.27</v>
+        <v>11.515</v>
       </c>
       <c r="G48">
         <v>8.48</v>
@@ -5327,28 +5327,28 @@
         <v>4.15</v>
       </c>
       <c r="M48">
-        <v>0.6119610000000001</v>
+        <v>0.6252645</v>
       </c>
       <c r="N48">
-        <v>3.538039</v>
+        <v>3.5247355</v>
       </c>
       <c r="O48">
-        <v>0.8137489700000001</v>
+        <v>0.8106891650000001</v>
       </c>
       <c r="P48">
-        <v>2.72429003</v>
+        <v>2.714046335</v>
       </c>
       <c r="Q48">
-        <v>3.49429003</v>
+        <v>3.484046334999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1792726914083814</v>
+        <v>0.1814412572263457</v>
       </c>
       <c r="T48">
-        <v>2.064780086685086</v>
+        <v>2.098327110202418</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.781477904637714</v>
+        <v>6.637191140709252</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5373,22 +5373,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1158150363299632</v>
+        <v>0.1155897592994005</v>
       </c>
       <c r="C49">
-        <v>13.9773471915297</v>
+        <v>13.75479842851912</v>
       </c>
       <c r="D49">
-        <v>17.0123471915297</v>
+        <v>17.03479842851912</v>
       </c>
       <c r="E49">
-        <v>11.515</v>
+        <v>11.76</v>
       </c>
       <c r="F49">
-        <v>11.515</v>
+        <v>11.76</v>
       </c>
       <c r="G49">
         <v>8.48</v>
@@ -5409,28 +5409,28 @@
         <v>4.15</v>
       </c>
       <c r="M49">
-        <v>0.6252645</v>
+        <v>0.6385680000000001</v>
       </c>
       <c r="N49">
-        <v>3.5247355</v>
+        <v>3.511432</v>
       </c>
       <c r="O49">
-        <v>0.8106891650000001</v>
+        <v>0.8076293600000001</v>
       </c>
       <c r="P49">
-        <v>2.714046335</v>
+        <v>2.70380264</v>
       </c>
       <c r="Q49">
-        <v>3.484046334999999</v>
+        <v>3.47380264</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1814412572263457</v>
+        <v>0.183693229421924</v>
       </c>
       <c r="T49">
-        <v>2.098327110202418</v>
+        <v>2.133164403855032</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.637191140709252</v>
+        <v>6.498916325277808</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1155897592994004</v>
+        <v>0.1153644822688377</v>
       </c>
       <c r="C50">
-        <v>13.75479842851912</v>
+        <v>13.53230900172152</v>
       </c>
       <c r="D50">
-        <v>17.03479842851912</v>
+        <v>17.05730900172151</v>
       </c>
       <c r="E50">
-        <v>11.76</v>
+        <v>12.005</v>
       </c>
       <c r="F50">
-        <v>11.76</v>
+        <v>12.005</v>
       </c>
       <c r="G50">
         <v>8.48</v>
@@ -5491,28 +5491,28 @@
         <v>4.15</v>
       </c>
       <c r="M50">
-        <v>0.638568</v>
+        <v>0.6518714999999999</v>
       </c>
       <c r="N50">
-        <v>3.511432</v>
+        <v>3.4981285</v>
       </c>
       <c r="O50">
-        <v>0.8076293600000001</v>
+        <v>0.8045695550000002</v>
       </c>
       <c r="P50">
-        <v>2.70380264</v>
+        <v>2.693558945</v>
       </c>
       <c r="Q50">
-        <v>3.47380264</v>
+        <v>3.463558945</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.183693229421924</v>
+        <v>0.1860335142526229</v>
       </c>
       <c r="T50">
-        <v>2.133164403855032</v>
+        <v>2.16936786588618</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.498916325277809</v>
+        <v>6.366285379863977</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5537,22 +5537,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1153644822688377</v>
+        <v>0.115139205238275</v>
       </c>
       <c r="C51">
-        <v>13.53230900172152</v>
+        <v>13.30987914667701</v>
       </c>
       <c r="D51">
-        <v>17.05730900172151</v>
+        <v>17.079879146677</v>
       </c>
       <c r="E51">
-        <v>12.005</v>
+        <v>12.25</v>
       </c>
       <c r="F51">
-        <v>12.005</v>
+        <v>12.25</v>
       </c>
       <c r="G51">
         <v>8.48</v>
@@ -5573,28 +5573,28 @@
         <v>4.15</v>
       </c>
       <c r="M51">
-        <v>0.6518714999999999</v>
+        <v>0.665175</v>
       </c>
       <c r="N51">
-        <v>3.4981285</v>
+        <v>3.484825</v>
       </c>
       <c r="O51">
-        <v>0.8045695550000002</v>
+        <v>0.8015097500000001</v>
       </c>
       <c r="P51">
-        <v>2.693558945</v>
+        <v>2.68331525</v>
       </c>
       <c r="Q51">
-        <v>3.463558945</v>
+        <v>3.45331525</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1860335142526229</v>
+        <v>0.1884674104765499</v>
       </c>
       <c r="T51">
-        <v>2.16936786588618</v>
+        <v>2.207019466398574</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.366285379863977</v>
+        <v>6.238959672266698</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5619,22 +5619,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.115139205238275</v>
+        <v>0.1149139282077122</v>
       </c>
       <c r="C52">
-        <v>13.30987914667701</v>
+        <v>13.08750910017404</v>
       </c>
       <c r="D52">
-        <v>17.079879146677</v>
+        <v>17.10250910017404</v>
       </c>
       <c r="E52">
-        <v>12.25</v>
+        <v>12.495</v>
       </c>
       <c r="F52">
-        <v>12.25</v>
+        <v>12.495</v>
       </c>
       <c r="G52">
         <v>8.48</v>
@@ -5655,28 +5655,28 @@
         <v>4.15</v>
       </c>
       <c r="M52">
-        <v>0.665175</v>
+        <v>0.6784785000000001</v>
       </c>
       <c r="N52">
-        <v>3.484825</v>
+        <v>3.4715215</v>
       </c>
       <c r="O52">
-        <v>0.8015097500000001</v>
+        <v>0.7984499450000001</v>
       </c>
       <c r="P52">
-        <v>2.68331525</v>
+        <v>2.673071555</v>
       </c>
       <c r="Q52">
-        <v>3.45331525</v>
+        <v>3.443071555</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1884674104765499</v>
+        <v>0.1910006494034943</v>
       </c>
       <c r="T52">
-        <v>2.207019466398574</v>
+        <v>2.246207866931882</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.238959672266698</v>
+        <v>6.116627129673232</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5701,22 +5701,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1149139282077122</v>
+        <v>0.1150890511771495</v>
       </c>
       <c r="C53">
-        <v>13.08750910017404</v>
+        <v>12.82491213326269</v>
       </c>
       <c r="D53">
-        <v>17.10250910017404</v>
+        <v>17.08491213326269</v>
       </c>
       <c r="E53">
-        <v>12.495</v>
+        <v>12.74</v>
       </c>
       <c r="F53">
-        <v>12.495</v>
+        <v>12.74</v>
       </c>
       <c r="G53">
         <v>8.48</v>
@@ -5737,45 +5737,45 @@
         <v>4.15</v>
       </c>
       <c r="M53">
-        <v>0.6784785000000001</v>
+        <v>0.704522</v>
       </c>
       <c r="N53">
-        <v>3.4715215</v>
+        <v>3.445478</v>
       </c>
       <c r="O53">
-        <v>0.7984499450000001</v>
+        <v>0.7924599400000002</v>
       </c>
       <c r="P53">
-        <v>2.673071555</v>
+        <v>2.65301806</v>
       </c>
       <c r="Q53">
-        <v>3.443071555</v>
+        <v>3.42301806</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1910006494034943</v>
+        <v>0.1936394399523947</v>
       </c>
       <c r="T53">
-        <v>2.246207866931882</v>
+        <v>2.287029117487412</v>
       </c>
       <c r="U53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.23</v>
       </c>
       <c r="W53">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.116627129673232</v>
+        <v>5.890518677912117</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5783,22 +5783,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1150890511771495</v>
+        <v>0.1148714741465867</v>
       </c>
       <c r="C54">
-        <v>12.82491213326269</v>
+        <v>12.60178049265443</v>
       </c>
       <c r="D54">
-        <v>17.08491213326269</v>
+        <v>17.10678049265443</v>
       </c>
       <c r="E54">
-        <v>12.74</v>
+        <v>12.985</v>
       </c>
       <c r="F54">
-        <v>12.74</v>
+        <v>12.985</v>
       </c>
       <c r="G54">
         <v>8.48</v>
@@ -5819,28 +5819,28 @@
         <v>4.15</v>
       </c>
       <c r="M54">
-        <v>0.704522</v>
+        <v>0.7180705000000001</v>
       </c>
       <c r="N54">
-        <v>3.445478</v>
+        <v>3.4319295</v>
       </c>
       <c r="O54">
-        <v>0.7924599400000002</v>
+        <v>0.7893437850000001</v>
       </c>
       <c r="P54">
-        <v>2.65301806</v>
+        <v>2.642585715</v>
       </c>
       <c r="Q54">
-        <v>3.42301806</v>
+        <v>3.412585715</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1936394399523947</v>
+        <v>0.1963905194608228</v>
       </c>
       <c r="T54">
-        <v>2.287029117487412</v>
+        <v>2.329587442534665</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.890518677912117</v>
+        <v>5.779376816064718</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5865,22 +5865,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1148714741465867</v>
+        <v>0.114653897116024</v>
       </c>
       <c r="C55">
-        <v>12.60178049265443</v>
+        <v>12.37870490595411</v>
       </c>
       <c r="D55">
-        <v>17.10678049265443</v>
+        <v>17.12870490595411</v>
       </c>
       <c r="E55">
-        <v>12.985</v>
+        <v>13.23</v>
       </c>
       <c r="F55">
-        <v>12.985</v>
+        <v>13.23</v>
       </c>
       <c r="G55">
         <v>8.48</v>
@@ -5901,28 +5901,28 @@
         <v>4.15</v>
       </c>
       <c r="M55">
-        <v>0.7180705000000001</v>
+        <v>0.731619</v>
       </c>
       <c r="N55">
-        <v>3.4319295</v>
+        <v>3.418381</v>
       </c>
       <c r="O55">
-        <v>0.7893437850000001</v>
+        <v>0.7862276300000001</v>
       </c>
       <c r="P55">
-        <v>2.642585715</v>
+        <v>2.63215337</v>
       </c>
       <c r="Q55">
-        <v>3.412585715</v>
+        <v>3.40215337</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1963905194608228</v>
+        <v>0.1992612111217912</v>
       </c>
       <c r="T55">
-        <v>2.329587442534665</v>
+        <v>2.373996129540495</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.779376816064718</v>
+        <v>5.672351319470927</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5947,22 +5947,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.114653897116024</v>
+        <v>0.1144363200854612</v>
       </c>
       <c r="C56">
-        <v>12.37870490595411</v>
+        <v>12.15568558895794</v>
       </c>
       <c r="D56">
-        <v>17.12870490595411</v>
+        <v>17.15068558895794</v>
       </c>
       <c r="E56">
-        <v>13.23</v>
+        <v>13.475</v>
       </c>
       <c r="F56">
-        <v>13.23</v>
+        <v>13.475</v>
       </c>
       <c r="G56">
         <v>8.48</v>
@@ -5983,28 +5983,28 @@
         <v>4.15</v>
       </c>
       <c r="M56">
-        <v>0.731619</v>
+        <v>0.7451675000000001</v>
       </c>
       <c r="N56">
-        <v>3.418381</v>
+        <v>3.4048325</v>
       </c>
       <c r="O56">
-        <v>0.7862276300000001</v>
+        <v>0.7831114750000001</v>
       </c>
       <c r="P56">
-        <v>2.63215337</v>
+        <v>2.621721025</v>
       </c>
       <c r="Q56">
-        <v>3.40215337</v>
+        <v>3.391721025</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1992612111217912</v>
+        <v>0.2022594890788027</v>
       </c>
       <c r="T56">
-        <v>2.373996129540495</v>
+        <v>2.420378535968807</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.672351319470927</v>
+        <v>5.56921765911691</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6029,22 +6029,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1144363200854612</v>
+        <v>0.1142187430548985</v>
       </c>
       <c r="C57">
-        <v>12.15568558895794</v>
+        <v>11.93272275857125</v>
       </c>
       <c r="D57">
-        <v>17.15068558895794</v>
+        <v>17.17272275857125</v>
       </c>
       <c r="E57">
-        <v>13.475</v>
+        <v>13.72</v>
       </c>
       <c r="F57">
-        <v>13.475</v>
+        <v>13.72</v>
       </c>
       <c r="G57">
         <v>8.48</v>
@@ -6065,28 +6065,28 @@
         <v>4.15</v>
       </c>
       <c r="M57">
-        <v>0.7451675000000001</v>
+        <v>0.7587160000000001</v>
       </c>
       <c r="N57">
-        <v>3.4048325</v>
+        <v>3.391284</v>
       </c>
       <c r="O57">
-        <v>0.7831114750000001</v>
+        <v>0.77999532</v>
       </c>
       <c r="P57">
-        <v>2.621721025</v>
+        <v>2.61128868</v>
       </c>
       <c r="Q57">
-        <v>3.391721025</v>
+        <v>3.38128868</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2022594890788027</v>
+        <v>0.2053940523974966</v>
       </c>
       <c r="T57">
-        <v>2.420378535968807</v>
+        <v>2.468869233598405</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.56921765911691</v>
+        <v>5.469767343775536</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1142187430548985</v>
+        <v>0.1140011660243357</v>
       </c>
       <c r="C58">
-        <v>11.93272275857125</v>
+        <v>11.70981663281562</v>
       </c>
       <c r="D58">
-        <v>17.17272275857125</v>
+        <v>17.19481663281562</v>
       </c>
       <c r="E58">
-        <v>13.72</v>
+        <v>13.965</v>
       </c>
       <c r="F58">
-        <v>13.72</v>
+        <v>13.965</v>
       </c>
       <c r="G58">
         <v>8.48</v>
@@ -6147,28 +6147,28 @@
         <v>4.15</v>
       </c>
       <c r="M58">
-        <v>0.7587160000000001</v>
+        <v>0.7722645000000001</v>
       </c>
       <c r="N58">
-        <v>3.391284</v>
+        <v>3.3777355</v>
       </c>
       <c r="O58">
-        <v>0.77999532</v>
+        <v>0.776879165</v>
       </c>
       <c r="P58">
-        <v>2.61128868</v>
+        <v>2.600856335</v>
       </c>
       <c r="Q58">
-        <v>3.38128868</v>
+        <v>3.370856335</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2053940523974966</v>
+        <v>0.2086744093589203</v>
       </c>
       <c r="T58">
-        <v>2.468869233598405</v>
+        <v>2.519615312513101</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.469767343775536</v>
+        <v>5.373806513182982</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6193,22 +6193,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1140011660243357</v>
+        <v>0.113783588993773</v>
       </c>
       <c r="C59">
-        <v>11.70981663281562</v>
+        <v>11.48696743083606</v>
       </c>
       <c r="D59">
-        <v>17.19481663281562</v>
+        <v>17.21696743083606</v>
       </c>
       <c r="E59">
-        <v>13.965</v>
+        <v>14.21</v>
       </c>
       <c r="F59">
-        <v>13.965</v>
+        <v>14.21</v>
       </c>
       <c r="G59">
         <v>8.48</v>
@@ -6229,28 +6229,28 @@
         <v>4.15</v>
       </c>
       <c r="M59">
-        <v>0.7722645000000001</v>
+        <v>0.7858130000000001</v>
       </c>
       <c r="N59">
-        <v>3.3777355</v>
+        <v>3.364187</v>
       </c>
       <c r="O59">
-        <v>0.776879165</v>
+        <v>0.7737630100000001</v>
       </c>
       <c r="P59">
-        <v>2.600856335</v>
+        <v>2.59042399</v>
       </c>
       <c r="Q59">
-        <v>3.370856335</v>
+        <v>3.36042399</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2086744093589203</v>
+        <v>0.2121109737946976</v>
       </c>
       <c r="T59">
-        <v>2.519615312513101</v>
+        <v>2.572777871376116</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.373806513182982</v>
+        <v>5.281154676748794</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6275,22 +6275,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.113783588993773</v>
+        <v>0.1135660119632102</v>
       </c>
       <c r="C60">
-        <v>11.48696743083605</v>
+        <v>11.2641753729083</v>
       </c>
       <c r="D60">
-        <v>17.21696743083605</v>
+        <v>17.2391753729083</v>
       </c>
       <c r="E60">
-        <v>14.21</v>
+        <v>14.455</v>
       </c>
       <c r="F60">
-        <v>14.21</v>
+        <v>14.455</v>
       </c>
       <c r="G60">
         <v>8.48</v>
@@ -6311,28 +6311,28 @@
         <v>4.15</v>
       </c>
       <c r="M60">
-        <v>0.785813</v>
+        <v>0.7993615000000001</v>
       </c>
       <c r="N60">
-        <v>3.364187</v>
+        <v>3.350638500000001</v>
       </c>
       <c r="O60">
-        <v>0.7737630100000001</v>
+        <v>0.7706468550000002</v>
       </c>
       <c r="P60">
-        <v>2.59042399</v>
+        <v>2.579991645</v>
       </c>
       <c r="Q60">
-        <v>3.36042399</v>
+        <v>3.349991645</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2121109737946976</v>
+        <v>0.2157151755200249</v>
       </c>
       <c r="T60">
-        <v>2.572777871376116</v>
+        <v>2.628533725793424</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.281154676748795</v>
+        <v>5.191643580532713</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6357,22 +6357,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1135660119632102</v>
+        <v>0.1133484349326475</v>
       </c>
       <c r="C61">
-        <v>11.2641753729083</v>
+        <v>11.04144068044603</v>
       </c>
       <c r="D61">
-        <v>17.2391753729083</v>
+        <v>17.26144068044603</v>
       </c>
       <c r="E61">
-        <v>14.455</v>
+        <v>14.7</v>
       </c>
       <c r="F61">
-        <v>14.455</v>
+        <v>14.7</v>
       </c>
       <c r="G61">
         <v>8.48</v>
@@ -6393,28 +6393,28 @@
         <v>4.15</v>
       </c>
       <c r="M61">
-        <v>0.7993615000000001</v>
+        <v>0.81291</v>
       </c>
       <c r="N61">
-        <v>3.350638500000001</v>
+        <v>3.33709</v>
       </c>
       <c r="O61">
-        <v>0.7706468550000002</v>
+        <v>0.7675307000000001</v>
       </c>
       <c r="P61">
-        <v>2.579991645</v>
+        <v>2.5695593</v>
       </c>
       <c r="Q61">
-        <v>3.349991645</v>
+        <v>3.3395593</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2157151755200249</v>
+        <v>0.2194995873316187</v>
       </c>
       <c r="T61">
-        <v>2.628533725793424</v>
+        <v>2.687077372931597</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.191643580532713</v>
+        <v>5.105116187523834</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6439,22 +6439,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1133484349326475</v>
+        <v>0.1131308579020847</v>
       </c>
       <c r="C62">
-        <v>11.04144068044603</v>
+        <v>10.81876357600832</v>
       </c>
       <c r="D62">
-        <v>17.26144068044603</v>
+        <v>17.28376357600832</v>
       </c>
       <c r="E62">
-        <v>14.7</v>
+        <v>14.945</v>
       </c>
       <c r="F62">
-        <v>14.7</v>
+        <v>14.945</v>
       </c>
       <c r="G62">
         <v>8.48</v>
@@ -6475,28 +6475,28 @@
         <v>4.15</v>
       </c>
       <c r="M62">
-        <v>0.81291</v>
+        <v>0.8264585000000001</v>
       </c>
       <c r="N62">
-        <v>3.33709</v>
+        <v>3.3235415</v>
       </c>
       <c r="O62">
-        <v>0.7675307000000001</v>
+        <v>0.7644145450000001</v>
       </c>
       <c r="P62">
-        <v>2.5695593</v>
+        <v>2.559126955</v>
       </c>
       <c r="Q62">
-        <v>3.3395593</v>
+        <v>3.329126955</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2194995873316187</v>
+        <v>0.223478071543807</v>
       </c>
       <c r="T62">
-        <v>2.687077372931597</v>
+        <v>2.748623258384549</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.105116187523834</v>
+        <v>5.021425758220165</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6521,22 +6521,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1131308579020847</v>
+        <v>0.112913280871522</v>
       </c>
       <c r="C63">
-        <v>10.81876357600832</v>
+        <v>10.59614428330697</v>
       </c>
       <c r="D63">
-        <v>17.28376357600832</v>
+        <v>17.30614428330697</v>
       </c>
       <c r="E63">
-        <v>14.945</v>
+        <v>15.19</v>
       </c>
       <c r="F63">
-        <v>14.945</v>
+        <v>15.19</v>
       </c>
       <c r="G63">
         <v>8.48</v>
@@ -6557,28 +6557,28 @@
         <v>4.15</v>
       </c>
       <c r="M63">
-        <v>0.8264585000000001</v>
+        <v>0.8400069999999999</v>
       </c>
       <c r="N63">
-        <v>3.3235415</v>
+        <v>3.309993</v>
       </c>
       <c r="O63">
-        <v>0.7644145450000001</v>
+        <v>0.7612983900000001</v>
       </c>
       <c r="P63">
-        <v>2.559126955</v>
+        <v>2.54869461</v>
       </c>
       <c r="Q63">
-        <v>3.329126955</v>
+        <v>3.31869461</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.223478071543807</v>
+        <v>0.2276659496619</v>
       </c>
       <c r="T63">
-        <v>2.748623258384549</v>
+        <v>2.813408400966604</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.021425758220165</v>
+        <v>4.940435020184356</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6603,22 +6603,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.112913280871522</v>
+        <v>0.1126957038409592</v>
       </c>
       <c r="C64">
-        <v>10.59614428330697</v>
+        <v>10.37358302721404</v>
       </c>
       <c r="D64">
-        <v>17.30614428330697</v>
+        <v>17.32858302721404</v>
       </c>
       <c r="E64">
-        <v>15.19</v>
+        <v>15.435</v>
       </c>
       <c r="F64">
-        <v>15.19</v>
+        <v>15.435</v>
       </c>
       <c r="G64">
         <v>8.48</v>
@@ -6639,28 +6639,28 @@
         <v>4.15</v>
       </c>
       <c r="M64">
-        <v>0.8400069999999999</v>
+        <v>0.8535555</v>
       </c>
       <c r="N64">
-        <v>3.309993</v>
+        <v>3.2964445</v>
       </c>
       <c r="O64">
-        <v>0.7612983900000001</v>
+        <v>0.758182235</v>
       </c>
       <c r="P64">
-        <v>2.54869461</v>
+        <v>2.538262265</v>
       </c>
       <c r="Q64">
-        <v>3.31869461</v>
+        <v>3.308262265</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2276659496619</v>
+        <v>0.2320801995701601</v>
       </c>
       <c r="T64">
-        <v>2.813408400966604</v>
+        <v>2.881695443147688</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.940435020184356</v>
+        <v>4.862015416689366</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6685,22 +6685,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1126957038409592</v>
+        <v>0.1124781268103965</v>
       </c>
       <c r="C65">
-        <v>10.37358302721404</v>
+        <v>10.15108003376936</v>
       </c>
       <c r="D65">
-        <v>17.32858302721404</v>
+        <v>17.35108003376936</v>
       </c>
       <c r="E65">
-        <v>15.435</v>
+        <v>15.68</v>
       </c>
       <c r="F65">
-        <v>15.435</v>
+        <v>15.68</v>
       </c>
       <c r="G65">
         <v>8.48</v>
@@ -6721,28 +6721,28 @@
         <v>4.15</v>
       </c>
       <c r="M65">
-        <v>0.8535555</v>
+        <v>0.867104</v>
       </c>
       <c r="N65">
-        <v>3.2964445</v>
+        <v>3.282896</v>
       </c>
       <c r="O65">
-        <v>0.758182235</v>
+        <v>0.7550660800000002</v>
       </c>
       <c r="P65">
-        <v>2.538262265</v>
+        <v>2.52782992</v>
       </c>
       <c r="Q65">
-        <v>3.308262265</v>
+        <v>3.29782992</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2320801995701601</v>
+        <v>0.2367396855844346</v>
       </c>
       <c r="T65">
-        <v>2.881695443147688</v>
+        <v>2.953776209894388</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.862015416689366</v>
+        <v>4.786046425803596</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6767,22 +6767,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1124781268103965</v>
+        <v>0.1122605497798337</v>
       </c>
       <c r="C66">
-        <v>10.15108003376936</v>
+        <v>9.928635530188117</v>
       </c>
       <c r="D66">
-        <v>17.35108003376936</v>
+        <v>17.37363553018812</v>
       </c>
       <c r="E66">
-        <v>15.68</v>
+        <v>15.925</v>
       </c>
       <c r="F66">
-        <v>15.68</v>
+        <v>15.925</v>
       </c>
       <c r="G66">
         <v>8.48</v>
@@ -6803,28 +6803,28 @@
         <v>4.15</v>
       </c>
       <c r="M66">
-        <v>0.867104</v>
+        <v>0.8806525000000001</v>
       </c>
       <c r="N66">
-        <v>3.282896</v>
+        <v>3.2693475</v>
       </c>
       <c r="O66">
-        <v>0.7550660800000002</v>
+        <v>0.7519499250000001</v>
       </c>
       <c r="P66">
-        <v>2.52782992</v>
+        <v>2.517397575</v>
       </c>
       <c r="Q66">
-        <v>3.29782992</v>
+        <v>3.287397575</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2367396855844346</v>
+        <v>0.2416654279423821</v>
       </c>
       <c r="T66">
-        <v>2.953776209894388</v>
+        <v>3.029975877598043</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.786046425803596</v>
+        <v>4.712414942329693</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6849,22 +6849,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1122605497798337</v>
+        <v>0.112042972749271</v>
       </c>
       <c r="C67">
-        <v>9.928635530188117</v>
+        <v>9.706249744868497</v>
       </c>
       <c r="D67">
-        <v>17.37363553018812</v>
+        <v>17.3962497448685</v>
       </c>
       <c r="E67">
-        <v>15.925</v>
+        <v>16.17</v>
       </c>
       <c r="F67">
-        <v>15.925</v>
+        <v>16.17</v>
       </c>
       <c r="G67">
         <v>8.48</v>
@@ -6885,28 +6885,28 @@
         <v>4.15</v>
       </c>
       <c r="M67">
-        <v>0.8806525000000001</v>
+        <v>0.8942010000000001</v>
       </c>
       <c r="N67">
-        <v>3.2693475</v>
+        <v>3.255799</v>
       </c>
       <c r="O67">
-        <v>0.7519499250000001</v>
+        <v>0.7488337700000001</v>
       </c>
       <c r="P67">
-        <v>2.517397575</v>
+        <v>2.50696523</v>
       </c>
       <c r="Q67">
-        <v>3.287397575</v>
+        <v>3.27696523</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2416654279423821</v>
+        <v>0.246880919850797</v>
       </c>
       <c r="T67">
-        <v>3.029975877598043</v>
+        <v>3.11065787869603</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.712414942329693</v>
+        <v>4.641014715930758</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6931,22 +6931,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.112042972749271</v>
+        <v>0.1118253957187082</v>
       </c>
       <c r="C68">
-        <v>9.706249744868497</v>
+        <v>9.483922907399418</v>
       </c>
       <c r="D68">
-        <v>17.3962497448685</v>
+        <v>17.41892290739942</v>
       </c>
       <c r="E68">
-        <v>16.17</v>
+        <v>16.415</v>
       </c>
       <c r="F68">
-        <v>16.17</v>
+        <v>16.415</v>
       </c>
       <c r="G68">
         <v>8.48</v>
@@ -6967,28 +6967,28 @@
         <v>4.15</v>
       </c>
       <c r="M68">
-        <v>0.8942010000000001</v>
+        <v>0.9077495000000002</v>
       </c>
       <c r="N68">
-        <v>3.255799</v>
+        <v>3.2422505</v>
       </c>
       <c r="O68">
-        <v>0.7488337700000001</v>
+        <v>0.745717615</v>
       </c>
       <c r="P68">
-        <v>2.50696523</v>
+        <v>2.496532885</v>
       </c>
       <c r="Q68">
-        <v>3.27696523</v>
+        <v>3.266532884999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.246880919850797</v>
+        <v>0.2524125021779037</v>
       </c>
       <c r="T68">
-        <v>3.11065787869603</v>
+        <v>3.19622969804238</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.641014715930758</v>
+        <v>4.571745839573582</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7013,22 +7013,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1118253957187082</v>
+        <v>0.1116078186881455</v>
       </c>
       <c r="C69">
-        <v>9.483922907399418</v>
+        <v>9.261655248568282</v>
       </c>
       <c r="D69">
-        <v>17.41892290739942</v>
+        <v>17.44165524856828</v>
       </c>
       <c r="E69">
-        <v>16.415</v>
+        <v>16.66</v>
       </c>
       <c r="F69">
-        <v>16.415</v>
+        <v>16.66</v>
       </c>
       <c r="G69">
         <v>8.48</v>
@@ -7049,28 +7049,28 @@
         <v>4.15</v>
       </c>
       <c r="M69">
-        <v>0.9077495000000002</v>
+        <v>0.9212980000000001</v>
       </c>
       <c r="N69">
-        <v>3.2422505</v>
+        <v>3.228702</v>
       </c>
       <c r="O69">
-        <v>0.745717615</v>
+        <v>0.74260146</v>
       </c>
       <c r="P69">
-        <v>2.496532885</v>
+        <v>2.48610054</v>
       </c>
       <c r="Q69">
-        <v>3.266532884999999</v>
+        <v>3.25610054</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2524125021779037</v>
+        <v>0.2582898084004547</v>
       </c>
       <c r="T69">
-        <v>3.19622969804238</v>
+        <v>3.287149756097877</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.571745839573582</v>
+        <v>4.504514283109265</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7095,22 +7095,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1116078186881455</v>
+        <v>0.1127184916575827</v>
       </c>
       <c r="C70">
-        <v>9.261655248568282</v>
+        <v>8.901230189502527</v>
       </c>
       <c r="D70">
-        <v>17.44165524856828</v>
+        <v>17.32623018950253</v>
       </c>
       <c r="E70">
-        <v>16.66</v>
+        <v>16.905</v>
       </c>
       <c r="F70">
-        <v>16.66</v>
+        <v>16.905</v>
       </c>
       <c r="G70">
         <v>8.48</v>
@@ -7131,45 +7131,45 @@
         <v>4.15</v>
       </c>
       <c r="M70">
-        <v>0.9212980000000001</v>
+        <v>0.9771090000000001</v>
       </c>
       <c r="N70">
-        <v>3.228702</v>
+        <v>3.172891</v>
       </c>
       <c r="O70">
-        <v>0.74260146</v>
+        <v>0.7297649300000001</v>
       </c>
       <c r="P70">
-        <v>2.48610054</v>
+        <v>2.44312607</v>
       </c>
       <c r="Q70">
-        <v>3.25610054</v>
+        <v>3.21312607</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2582898084004547</v>
+        <v>0.2645462956696218</v>
       </c>
       <c r="T70">
-        <v>3.287149756097877</v>
+        <v>3.383935624350503</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.23</v>
       </c>
       <c r="W70">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.504514283109265</v>
+        <v>4.247223185949572</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7177,22 +7177,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1127184916575827</v>
+        <v>0.11252016462702</v>
       </c>
       <c r="C71">
-        <v>8.901230189502527</v>
+        <v>8.676728860481443</v>
       </c>
       <c r="D71">
-        <v>17.32623018950253</v>
+        <v>17.34672886048144</v>
       </c>
       <c r="E71">
-        <v>16.905</v>
+        <v>17.15</v>
       </c>
       <c r="F71">
-        <v>16.905</v>
+        <v>17.15</v>
       </c>
       <c r="G71">
         <v>8.48</v>
@@ -7213,28 +7213,28 @@
         <v>4.15</v>
       </c>
       <c r="M71">
-        <v>0.9771090000000001</v>
+        <v>0.9912700000000002</v>
       </c>
       <c r="N71">
-        <v>3.172891</v>
+        <v>3.15873</v>
       </c>
       <c r="O71">
-        <v>0.7297649300000001</v>
+        <v>0.7265079000000001</v>
       </c>
       <c r="P71">
-        <v>2.44312607</v>
+        <v>2.4322221</v>
       </c>
       <c r="Q71">
-        <v>3.21312607</v>
+        <v>3.2022221</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2645462956696218</v>
+        <v>0.2712198820900666</v>
       </c>
       <c r="T71">
-        <v>3.383935624350503</v>
+        <v>3.48717388381997</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.247223185949572</v>
+        <v>4.186548569007435</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7259,22 +7259,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.11252016462702</v>
+        <v>0.1123218375964573</v>
       </c>
       <c r="C72">
-        <v>8.676728860481443</v>
+        <v>8.452276092887708</v>
       </c>
       <c r="D72">
-        <v>17.34672886048144</v>
+        <v>17.36727609288771</v>
       </c>
       <c r="E72">
-        <v>17.15</v>
+        <v>17.395</v>
       </c>
       <c r="F72">
-        <v>17.15</v>
+        <v>17.395</v>
       </c>
       <c r="G72">
         <v>8.48</v>
@@ -7295,28 +7295,28 @@
         <v>4.15</v>
       </c>
       <c r="M72">
-        <v>0.9912700000000002</v>
+        <v>1.005431</v>
       </c>
       <c r="N72">
-        <v>3.15873</v>
+        <v>3.144569</v>
       </c>
       <c r="O72">
-        <v>0.7265079000000001</v>
+        <v>0.7232508700000001</v>
       </c>
       <c r="P72">
-        <v>2.4322221</v>
+        <v>2.42131813</v>
       </c>
       <c r="Q72">
-        <v>3.2022221</v>
+        <v>3.19131813</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2712198820900666</v>
+        <v>0.2783537158498526</v>
       </c>
       <c r="T72">
-        <v>3.48717388381997</v>
+        <v>3.59753202325285</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.186548569007435</v>
+        <v>4.127583096204512</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7341,22 +7341,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1123218375964573</v>
+        <v>0.1121235105658945</v>
       </c>
       <c r="C73">
-        <v>8.452276092887711</v>
+        <v>8.227872059489265</v>
       </c>
       <c r="D73">
-        <v>17.36727609288771</v>
+        <v>17.38787205948926</v>
       </c>
       <c r="E73">
-        <v>17.395</v>
+        <v>17.64</v>
       </c>
       <c r="F73">
-        <v>17.395</v>
+        <v>17.64</v>
       </c>
       <c r="G73">
         <v>8.48</v>
@@ -7377,28 +7377,28 @@
         <v>4.15</v>
       </c>
       <c r="M73">
-        <v>1.005431</v>
+        <v>1.019592</v>
       </c>
       <c r="N73">
-        <v>3.144569000000001</v>
+        <v>3.130408</v>
       </c>
       <c r="O73">
-        <v>0.7232508700000002</v>
+        <v>0.71999384</v>
       </c>
       <c r="P73">
-        <v>2.42131813</v>
+        <v>2.41041416</v>
       </c>
       <c r="Q73">
-        <v>3.19131813</v>
+        <v>3.18041416</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2783537158498525</v>
+        <v>0.2859971091639089</v>
       </c>
       <c r="T73">
-        <v>3.597532023252848</v>
+        <v>3.715772886930932</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.127583096204514</v>
+        <v>4.070255553201672</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7423,22 +7423,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1121235105658945</v>
+        <v>0.1119251835353318</v>
       </c>
       <c r="C74">
-        <v>8.227872059489265</v>
+        <v>8.003516933874572</v>
       </c>
       <c r="D74">
-        <v>17.38787205948926</v>
+        <v>17.40851693387457</v>
       </c>
       <c r="E74">
-        <v>17.64</v>
+        <v>17.885</v>
       </c>
       <c r="F74">
-        <v>17.64</v>
+        <v>17.885</v>
       </c>
       <c r="G74">
         <v>8.48</v>
@@ -7459,28 +7459,28 @@
         <v>4.15</v>
       </c>
       <c r="M74">
-        <v>1.019592</v>
+        <v>1.033753</v>
       </c>
       <c r="N74">
-        <v>3.130408</v>
+        <v>3.116247</v>
       </c>
       <c r="O74">
-        <v>0.71999384</v>
+        <v>0.7167368100000001</v>
       </c>
       <c r="P74">
-        <v>2.41041416</v>
+        <v>2.39951019</v>
       </c>
       <c r="Q74">
-        <v>3.18041416</v>
+        <v>3.16951019</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2859971091639089</v>
+        <v>0.2942066797604879</v>
       </c>
       <c r="T74">
-        <v>3.715772886930932</v>
+        <v>3.84277233310369</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.070255553201672</v>
+        <v>4.01449862781535</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7505,22 +7505,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1119251835353318</v>
+        <v>0.113721156504769</v>
       </c>
       <c r="C75">
-        <v>8.003516933874572</v>
+        <v>7.573334017516508</v>
       </c>
       <c r="D75">
-        <v>17.40851693387457</v>
+        <v>17.22333401751651</v>
       </c>
       <c r="E75">
-        <v>17.885</v>
+        <v>18.13</v>
       </c>
       <c r="F75">
-        <v>17.885</v>
+        <v>18.13</v>
       </c>
       <c r="G75">
         <v>8.48</v>
@@ -7541,45 +7541,45 @@
         <v>4.15</v>
       </c>
       <c r="M75">
-        <v>1.033753</v>
+        <v>1.111369</v>
       </c>
       <c r="N75">
-        <v>3.116247</v>
+        <v>3.038631000000001</v>
       </c>
       <c r="O75">
-        <v>0.7167368100000001</v>
+        <v>0.6988851300000002</v>
       </c>
       <c r="P75">
-        <v>2.39951019</v>
+        <v>2.33974587</v>
       </c>
       <c r="Q75">
-        <v>3.16951019</v>
+        <v>3.10974587</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2942066797604879</v>
+        <v>0.303047755787573</v>
       </c>
       <c r="T75">
-        <v>3.84277233310369</v>
+        <v>3.979540967443582</v>
       </c>
       <c r="U75">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V75">
         <v>0.23</v>
       </c>
       <c r="W75">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.01449862781535</v>
+        <v>3.734133307659293</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7587,22 +7587,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.113721156504769</v>
+        <v>0.1135497794742062</v>
       </c>
       <c r="C76">
-        <v>7.573334017516508</v>
+        <v>7.345834509009457</v>
       </c>
       <c r="D76">
-        <v>17.22333401751651</v>
+        <v>17.24083450900946</v>
       </c>
       <c r="E76">
-        <v>18.13</v>
+        <v>18.375</v>
       </c>
       <c r="F76">
-        <v>18.13</v>
+        <v>18.375</v>
       </c>
       <c r="G76">
         <v>8.48</v>
@@ -7623,28 +7623,28 @@
         <v>4.15</v>
       </c>
       <c r="M76">
-        <v>1.111369</v>
+        <v>1.1263875</v>
       </c>
       <c r="N76">
-        <v>3.038631000000001</v>
+        <v>3.0236125</v>
       </c>
       <c r="O76">
-        <v>0.6988851300000002</v>
+        <v>0.6954308750000001</v>
       </c>
       <c r="P76">
-        <v>2.33974587</v>
+        <v>2.328181625</v>
       </c>
       <c r="Q76">
-        <v>3.10974587</v>
+        <v>3.098181625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.303047755787573</v>
+        <v>0.312596117896825</v>
       </c>
       <c r="T76">
-        <v>3.979540967443582</v>
+        <v>4.127251092530667</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.734133307659293</v>
+        <v>3.684344863557169</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7669,22 +7669,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1135497794742062</v>
+        <v>0.1133784024436435</v>
       </c>
       <c r="C77">
-        <v>7.345834509009457</v>
+        <v>7.118370600893641</v>
       </c>
       <c r="D77">
-        <v>17.24083450900946</v>
+        <v>17.25837060089364</v>
       </c>
       <c r="E77">
-        <v>18.375</v>
+        <v>18.62</v>
       </c>
       <c r="F77">
-        <v>18.375</v>
+        <v>18.62</v>
       </c>
       <c r="G77">
         <v>8.48</v>
@@ -7705,28 +7705,28 @@
         <v>4.15</v>
       </c>
       <c r="M77">
-        <v>1.1263875</v>
+        <v>1.141406</v>
       </c>
       <c r="N77">
-        <v>3.0236125</v>
+        <v>3.008594</v>
       </c>
       <c r="O77">
-        <v>0.6954308750000001</v>
+        <v>0.6919766200000002</v>
       </c>
       <c r="P77">
-        <v>2.328181625</v>
+        <v>2.31661738</v>
       </c>
       <c r="Q77">
-        <v>3.098181625</v>
+        <v>3.08661738</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.312596117896825</v>
+        <v>0.3229401768485146</v>
       </c>
       <c r="T77">
-        <v>4.127251092530667</v>
+        <v>4.287270394708341</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.684344863557169</v>
+        <v>3.635866641668258</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7751,22 +7751,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1133784024436435</v>
+        <v>0.1132070254130807</v>
       </c>
       <c r="C78">
-        <v>7.118370600893641</v>
+        <v>6.89094240190985</v>
       </c>
       <c r="D78">
-        <v>17.25837060089364</v>
+        <v>17.27594240190985</v>
       </c>
       <c r="E78">
-        <v>18.62</v>
+        <v>18.865</v>
       </c>
       <c r="F78">
-        <v>18.62</v>
+        <v>18.865</v>
       </c>
       <c r="G78">
         <v>8.48</v>
@@ -7787,28 +7787,28 @@
         <v>4.15</v>
       </c>
       <c r="M78">
-        <v>1.141406</v>
+        <v>1.1564245</v>
       </c>
       <c r="N78">
-        <v>3.008594</v>
+        <v>2.9935755</v>
       </c>
       <c r="O78">
-        <v>0.6919766200000002</v>
+        <v>0.6885223650000001</v>
       </c>
       <c r="P78">
-        <v>2.31661738</v>
+        <v>2.305053135000001</v>
       </c>
       <c r="Q78">
-        <v>3.08661738</v>
+        <v>3.075053135</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3229401768485146</v>
+        <v>0.3341837191873076</v>
       </c>
       <c r="T78">
-        <v>4.287270394708341</v>
+        <v>4.461204418814509</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.635866641668258</v>
+        <v>3.588647594373865</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7833,22 +7833,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1132070254130807</v>
+        <v>0.113035648382518</v>
       </c>
       <c r="C79">
-        <v>6.89094240190985</v>
+        <v>6.663550021242202</v>
       </c>
       <c r="D79">
-        <v>17.27594240190985</v>
+        <v>17.2935500212422</v>
       </c>
       <c r="E79">
-        <v>18.865</v>
+        <v>19.11</v>
       </c>
       <c r="F79">
-        <v>18.865</v>
+        <v>19.11</v>
       </c>
       <c r="G79">
         <v>8.48</v>
@@ -7869,28 +7869,28 @@
         <v>4.15</v>
       </c>
       <c r="M79">
-        <v>1.1564245</v>
+        <v>1.171443</v>
       </c>
       <c r="N79">
-        <v>2.9935755</v>
+        <v>2.978557</v>
       </c>
       <c r="O79">
-        <v>0.6885223650000001</v>
+        <v>0.6850681100000001</v>
       </c>
       <c r="P79">
-        <v>2.305053135000001</v>
+        <v>2.29348889</v>
       </c>
       <c r="Q79">
-        <v>3.075053135</v>
+        <v>3.06348889</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3341837191873076</v>
+        <v>0.3464494017387182</v>
       </c>
       <c r="T79">
-        <v>4.461204418814509</v>
+        <v>4.650950626930329</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.588647594373865</v>
+        <v>3.542639291881893</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7915,22 +7915,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.113035648382518</v>
+        <v>0.1145675113519553</v>
       </c>
       <c r="C80">
-        <v>6.663550021242202</v>
+        <v>6.262425265773146</v>
       </c>
       <c r="D80">
-        <v>17.2935500212422</v>
+        <v>17.13742526577315</v>
       </c>
       <c r="E80">
-        <v>19.11</v>
+        <v>19.355</v>
       </c>
       <c r="F80">
-        <v>19.11</v>
+        <v>19.355</v>
       </c>
       <c r="G80">
         <v>8.48</v>
@@ -7951,45 +7951,45 @@
         <v>4.15</v>
       </c>
       <c r="M80">
-        <v>1.171443</v>
+        <v>1.2406555</v>
       </c>
       <c r="N80">
-        <v>2.978557</v>
+        <v>2.9093445</v>
       </c>
       <c r="O80">
-        <v>0.6850681100000001</v>
+        <v>0.6691492350000001</v>
       </c>
       <c r="P80">
-        <v>2.29348889</v>
+        <v>2.240195265000001</v>
       </c>
       <c r="Q80">
-        <v>3.06348889</v>
+        <v>3.010195265</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3464494017387182</v>
+        <v>0.3598832445331203</v>
       </c>
       <c r="T80">
-        <v>4.650950626930329</v>
+        <v>4.85876790248575</v>
       </c>
       <c r="U80">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V80">
         <v>0.23</v>
       </c>
       <c r="W80">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>3.542639291881893</v>
+        <v>3.345005926302668</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7997,22 +7997,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1145675113519553</v>
+        <v>0.1144176943213925</v>
       </c>
       <c r="C81">
-        <v>6.262425265773146</v>
+        <v>6.032569875321041</v>
       </c>
       <c r="D81">
-        <v>17.13742526577315</v>
+        <v>17.15256987532104</v>
       </c>
       <c r="E81">
-        <v>19.355</v>
+        <v>19.6</v>
       </c>
       <c r="F81">
-        <v>19.355</v>
+        <v>19.6</v>
       </c>
       <c r="G81">
         <v>8.48</v>
@@ -8033,28 +8033,28 @@
         <v>4.15</v>
       </c>
       <c r="M81">
-        <v>1.2406555</v>
+        <v>1.25636</v>
       </c>
       <c r="N81">
-        <v>2.9093445</v>
+        <v>2.89364</v>
       </c>
       <c r="O81">
-        <v>0.6691492350000001</v>
+        <v>0.6655372000000002</v>
       </c>
       <c r="P81">
-        <v>2.240195265000001</v>
+        <v>2.2281028</v>
       </c>
       <c r="Q81">
-        <v>3.010195265</v>
+        <v>2.9981028</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3598832445331203</v>
+        <v>0.3746604716069626</v>
       </c>
       <c r="T81">
-        <v>4.85876790248575</v>
+        <v>5.087366905596714</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.345005926302668</v>
+        <v>3.303193352223885</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8079,22 +8079,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1144176943213925</v>
+        <v>0.1142678772908298</v>
       </c>
       <c r="C82">
-        <v>6.032569875321041</v>
+        <v>5.802741275598851</v>
       </c>
       <c r="D82">
-        <v>17.15256987532104</v>
+        <v>17.16774127559885</v>
       </c>
       <c r="E82">
-        <v>19.6</v>
+        <v>19.845</v>
       </c>
       <c r="F82">
-        <v>19.6</v>
+        <v>19.845</v>
       </c>
       <c r="G82">
         <v>8.48</v>
@@ -8115,28 +8115,28 @@
         <v>4.15</v>
       </c>
       <c r="M82">
-        <v>1.25636</v>
+        <v>1.2720645</v>
       </c>
       <c r="N82">
-        <v>2.89364</v>
+        <v>2.8779355</v>
       </c>
       <c r="O82">
-        <v>0.6655372000000002</v>
+        <v>0.6619251650000001</v>
       </c>
       <c r="P82">
-        <v>2.2281028</v>
+        <v>2.216010335</v>
       </c>
       <c r="Q82">
-        <v>2.9981028</v>
+        <v>2.986010335</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3746604716069626</v>
+        <v>0.3909931962675252</v>
       </c>
       <c r="T82">
-        <v>5.087366905596714</v>
+        <v>5.340028961666727</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.303193352223885</v>
+        <v>3.262413187381615</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8161,22 +8161,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1142678772908298</v>
+        <v>0.114118060260267</v>
       </c>
       <c r="C83">
-        <v>5.802741275598851</v>
+        <v>5.572939537758508</v>
       </c>
       <c r="D83">
-        <v>17.16774127559885</v>
+        <v>17.18293953775851</v>
       </c>
       <c r="E83">
-        <v>19.845</v>
+        <v>20.09</v>
       </c>
       <c r="F83">
-        <v>19.845</v>
+        <v>20.09</v>
       </c>
       <c r="G83">
         <v>8.48</v>
@@ -8197,28 +8197,28 @@
         <v>4.15</v>
       </c>
       <c r="M83">
-        <v>1.2720645</v>
+        <v>1.287769</v>
       </c>
       <c r="N83">
-        <v>2.8779355</v>
+        <v>2.862231</v>
       </c>
       <c r="O83">
-        <v>0.6619251650000001</v>
+        <v>0.6583131300000001</v>
       </c>
       <c r="P83">
-        <v>2.216010335</v>
+        <v>2.20391787</v>
       </c>
       <c r="Q83">
-        <v>2.986010335</v>
+        <v>2.97391787</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3909931962675252</v>
+        <v>0.4091406681125946</v>
       </c>
       <c r="T83">
-        <v>5.340028961666727</v>
+        <v>5.620764579522296</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.262413187381615</v>
+        <v>3.222627660706229</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8243,22 +8243,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.114118060260267</v>
+        <v>0.1139682432297043</v>
       </c>
       <c r="C84">
-        <v>5.572939537758508</v>
+        <v>5.34316473320408</v>
       </c>
       <c r="D84">
-        <v>17.18293953775851</v>
+        <v>17.19816473320408</v>
       </c>
       <c r="E84">
-        <v>20.09</v>
+        <v>20.335</v>
       </c>
       <c r="F84">
-        <v>20.09</v>
+        <v>20.335</v>
       </c>
       <c r="G84">
         <v>8.48</v>
@@ -8279,28 +8279,28 @@
         <v>4.15</v>
       </c>
       <c r="M84">
-        <v>1.287769</v>
+        <v>1.3034735</v>
       </c>
       <c r="N84">
-        <v>2.862231</v>
+        <v>2.8465265</v>
       </c>
       <c r="O84">
-        <v>0.6583131300000001</v>
+        <v>0.6547010950000001</v>
       </c>
       <c r="P84">
-        <v>2.20391787</v>
+        <v>2.191825405</v>
       </c>
       <c r="Q84">
-        <v>2.97391787</v>
+        <v>2.961825405</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4091406681125946</v>
+        <v>0.4294231366453193</v>
       </c>
       <c r="T84">
-        <v>5.620764579522296</v>
+        <v>5.93452791712558</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.222627660706229</v>
+        <v>3.183800821420612</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8325,22 +8325,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1139682432297043</v>
+        <v>0.1138184261991415</v>
       </c>
       <c r="C85">
-        <v>5.34316473320408</v>
+        <v>5.113416933592973</v>
       </c>
       <c r="D85">
-        <v>17.19816473320408</v>
+        <v>17.21341693359297</v>
       </c>
       <c r="E85">
-        <v>20.335</v>
+        <v>20.58</v>
       </c>
       <c r="F85">
-        <v>20.335</v>
+        <v>20.58</v>
       </c>
       <c r="G85">
         <v>8.48</v>
@@ -8361,28 +8361,28 @@
         <v>4.15</v>
       </c>
       <c r="M85">
-        <v>1.3034735</v>
+        <v>1.319178</v>
       </c>
       <c r="N85">
-        <v>2.8465265</v>
+        <v>2.830822</v>
       </c>
       <c r="O85">
-        <v>0.6547010950000001</v>
+        <v>0.6510890600000001</v>
       </c>
       <c r="P85">
-        <v>2.191825405</v>
+        <v>2.17973294</v>
       </c>
       <c r="Q85">
-        <v>2.961825405</v>
+        <v>2.94973294</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4294231366453193</v>
+        <v>0.4522409137446347</v>
       </c>
       <c r="T85">
-        <v>5.93452791712558</v>
+        <v>6.287511671929275</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.183800821420612</v>
+        <v>3.145898430689414</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8407,22 +8407,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1138184261991415</v>
+        <v>0.1136686091685788</v>
       </c>
       <c r="C86">
-        <v>5.113416933592976</v>
+        <v>4.883696210837002</v>
       </c>
       <c r="D86">
-        <v>17.21341693359297</v>
+        <v>17.228696210837</v>
       </c>
       <c r="E86">
-        <v>20.58</v>
+        <v>20.825</v>
       </c>
       <c r="F86">
-        <v>20.58</v>
+        <v>20.825</v>
       </c>
       <c r="G86">
         <v>8.48</v>
@@ -8443,28 +8443,28 @@
         <v>4.15</v>
       </c>
       <c r="M86">
-        <v>1.319178</v>
+        <v>1.3348825</v>
       </c>
       <c r="N86">
-        <v>2.830822</v>
+        <v>2.8151175</v>
       </c>
       <c r="O86">
-        <v>0.6510890600000001</v>
+        <v>0.6474770250000002</v>
       </c>
       <c r="P86">
-        <v>2.17973294</v>
+        <v>2.167640475</v>
       </c>
       <c r="Q86">
-        <v>2.94973294</v>
+        <v>2.937640475</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4522409137446344</v>
+        <v>0.4781010611238584</v>
       </c>
       <c r="T86">
-        <v>6.287511671929271</v>
+        <v>6.687559927373457</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.145898430689415</v>
+        <v>3.108887860916598</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8489,22 +8489,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1136686091685788</v>
+        <v>0.113518792138016</v>
       </c>
       <c r="C87">
-        <v>4.883696210837002</v>
+        <v>4.654002637103531</v>
       </c>
       <c r="D87">
-        <v>17.228696210837</v>
+        <v>17.24400263710353</v>
       </c>
       <c r="E87">
-        <v>20.825</v>
+        <v>21.07</v>
       </c>
       <c r="F87">
-        <v>20.825</v>
+        <v>21.07</v>
       </c>
       <c r="G87">
         <v>8.48</v>
@@ -8525,28 +8525,28 @@
         <v>4.15</v>
       </c>
       <c r="M87">
-        <v>1.3348825</v>
+        <v>1.350587</v>
       </c>
       <c r="N87">
-        <v>2.8151175</v>
+        <v>2.799413</v>
       </c>
       <c r="O87">
-        <v>0.6474770250000002</v>
+        <v>0.6438649900000001</v>
       </c>
       <c r="P87">
-        <v>2.167640475</v>
+        <v>2.15554801</v>
       </c>
       <c r="Q87">
-        <v>2.937640475</v>
+        <v>2.92554801</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4781010611238584</v>
+        <v>0.5076555152715428</v>
       </c>
       <c r="T87">
-        <v>6.687559927373457</v>
+        <v>7.144757933595383</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.108887860916598</v>
+        <v>3.07273800206873</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8571,22 +8571,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.113518792138016</v>
+        <v>0.1133689751074533</v>
       </c>
       <c r="C88">
-        <v>4.654002637103531</v>
+        <v>4.424336284816615</v>
       </c>
       <c r="D88">
-        <v>17.24400263710353</v>
+        <v>17.25933628481662</v>
       </c>
       <c r="E88">
-        <v>21.07</v>
+        <v>21.315</v>
       </c>
       <c r="F88">
-        <v>21.07</v>
+        <v>21.315</v>
       </c>
       <c r="G88">
         <v>8.48</v>
@@ -8607,28 +8607,28 @@
         <v>4.15</v>
       </c>
       <c r="M88">
-        <v>1.350587</v>
+        <v>1.3662915</v>
       </c>
       <c r="N88">
-        <v>2.799413</v>
+        <v>2.7837085</v>
       </c>
       <c r="O88">
-        <v>0.6438649900000001</v>
+        <v>0.6402529550000001</v>
       </c>
       <c r="P88">
-        <v>2.15554801</v>
+        <v>2.143455545</v>
       </c>
       <c r="Q88">
-        <v>2.92554801</v>
+        <v>2.913455545</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5076555152715428</v>
+        <v>0.5417568085188712</v>
       </c>
       <c r="T88">
-        <v>7.144757933595383</v>
+        <v>7.672294094620684</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.07273800206873</v>
+        <v>3.037419174458745</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8653,22 +8653,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1133689751074533</v>
+        <v>0.1132191580768905</v>
       </c>
       <c r="C89">
-        <v>4.424336284816615</v>
+        <v>4.194697226658153</v>
       </c>
       <c r="D89">
-        <v>17.25933628481662</v>
+        <v>17.27469722665815</v>
       </c>
       <c r="E89">
-        <v>21.315</v>
+        <v>21.56</v>
       </c>
       <c r="F89">
-        <v>21.315</v>
+        <v>21.56</v>
       </c>
       <c r="G89">
         <v>8.48</v>
@@ -8689,28 +8689,28 @@
         <v>4.15</v>
       </c>
       <c r="M89">
-        <v>1.3662915</v>
+        <v>1.381996</v>
       </c>
       <c r="N89">
-        <v>2.7837085</v>
+        <v>2.768004</v>
       </c>
       <c r="O89">
-        <v>0.6402529550000001</v>
+        <v>0.6366409200000001</v>
       </c>
       <c r="P89">
-        <v>2.143455545</v>
+        <v>2.13136308</v>
       </c>
       <c r="Q89">
-        <v>2.913455545</v>
+        <v>2.90136308</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5417568085188712</v>
+        <v>0.5815416506407542</v>
       </c>
       <c r="T89">
-        <v>7.672294094620684</v>
+        <v>8.287752949150201</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.037419174458745</v>
+        <v>3.002903047476259</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8735,22 +8735,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1132191580768905</v>
+        <v>0.1184146810463277</v>
       </c>
       <c r="C90">
-        <v>4.194697226658153</v>
+        <v>3.432482810905718</v>
       </c>
       <c r="D90">
-        <v>17.27469722665815</v>
+        <v>16.75748281090572</v>
       </c>
       <c r="E90">
-        <v>21.56</v>
+        <v>21.805</v>
       </c>
       <c r="F90">
-        <v>21.56</v>
+        <v>21.805</v>
       </c>
       <c r="G90">
         <v>8.48</v>
@@ -8771,45 +8771,45 @@
         <v>4.15</v>
       </c>
       <c r="M90">
-        <v>1.381996</v>
+        <v>1.5677795</v>
       </c>
       <c r="N90">
-        <v>2.768004</v>
+        <v>2.5822205</v>
       </c>
       <c r="O90">
-        <v>0.6366409200000001</v>
+        <v>0.593910715</v>
       </c>
       <c r="P90">
-        <v>2.13136308</v>
+        <v>1.988309785</v>
       </c>
       <c r="Q90">
-        <v>2.90136308</v>
+        <v>2.758309785</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5815416506407542</v>
+        <v>0.6285601004211614</v>
       </c>
       <c r="T90">
-        <v>8.287752949150201</v>
+        <v>9.015113413594175</v>
       </c>
       <c r="U90">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V90">
         <v>0.23</v>
       </c>
       <c r="W90">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>3.002903047476259</v>
+        <v>2.647055915707534</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8817,22 +8817,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1184146810463277</v>
+        <v>0.118324924015765</v>
       </c>
       <c r="C91">
-        <v>3.432482810905718</v>
+        <v>3.196155082348866</v>
       </c>
       <c r="D91">
-        <v>16.75748281090572</v>
+        <v>16.76615508234887</v>
       </c>
       <c r="E91">
-        <v>21.805</v>
+        <v>22.05</v>
       </c>
       <c r="F91">
-        <v>21.805</v>
+        <v>22.05</v>
       </c>
       <c r="G91">
         <v>8.48</v>
@@ -8853,28 +8853,28 @@
         <v>4.15</v>
       </c>
       <c r="M91">
-        <v>1.5677795</v>
+        <v>1.585395</v>
       </c>
       <c r="N91">
-        <v>2.5822205</v>
+        <v>2.564605</v>
       </c>
       <c r="O91">
-        <v>0.593910715</v>
+        <v>0.5898591500000001</v>
       </c>
       <c r="P91">
-        <v>1.988309785</v>
+        <v>1.97474585</v>
       </c>
       <c r="Q91">
-        <v>2.758309785</v>
+        <v>2.74474585</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6285601004211614</v>
+        <v>0.6849822401576502</v>
       </c>
       <c r="T91">
-        <v>9.015113413594175</v>
+        <v>9.887945970926946</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.647055915707534</v>
+        <v>2.617644183310784</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8899,22 +8899,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.118324924015765</v>
+        <v>0.1182351669852023</v>
       </c>
       <c r="C92">
-        <v>3.196155082348866</v>
+        <v>2.959836334524326</v>
       </c>
       <c r="D92">
-        <v>16.76615508234887</v>
+        <v>16.77483633452433</v>
       </c>
       <c r="E92">
-        <v>22.05</v>
+        <v>22.295</v>
       </c>
       <c r="F92">
-        <v>22.05</v>
+        <v>22.295</v>
       </c>
       <c r="G92">
         <v>8.48</v>
@@ -8935,28 +8935,28 @@
         <v>4.15</v>
       </c>
       <c r="M92">
-        <v>1.585395</v>
+        <v>1.6030105</v>
       </c>
       <c r="N92">
-        <v>2.564605</v>
+        <v>2.5469895</v>
       </c>
       <c r="O92">
-        <v>0.5898591500000001</v>
+        <v>0.5858075850000001</v>
       </c>
       <c r="P92">
-        <v>1.97474585</v>
+        <v>1.961181915</v>
       </c>
       <c r="Q92">
-        <v>2.74474585</v>
+        <v>2.731181915</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6849822401576502</v>
+        <v>0.7539426331689142</v>
       </c>
       <c r="T92">
-        <v>9.887945970926946</v>
+        <v>10.95474131877811</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.617644183310784</v>
+        <v>2.588878862615061</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8981,22 +8981,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1182351669852023</v>
+        <v>0.1181454099546395</v>
       </c>
       <c r="C93">
-        <v>2.959836334524326</v>
+        <v>2.723526581389564</v>
       </c>
       <c r="D93">
-        <v>16.77483633452433</v>
+        <v>16.78352658138957</v>
       </c>
       <c r="E93">
-        <v>22.295</v>
+        <v>22.54</v>
       </c>
       <c r="F93">
-        <v>22.295</v>
+        <v>22.54</v>
       </c>
       <c r="G93">
         <v>8.48</v>
@@ -9017,28 +9017,28 @@
         <v>4.15</v>
       </c>
       <c r="M93">
-        <v>1.6030105</v>
+        <v>1.620626</v>
       </c>
       <c r="N93">
-        <v>2.5469895</v>
+        <v>2.529374</v>
       </c>
       <c r="O93">
-        <v>0.5858075850000001</v>
+        <v>0.5817560199999999</v>
       </c>
       <c r="P93">
-        <v>1.961181915</v>
+        <v>1.94761798</v>
       </c>
       <c r="Q93">
-        <v>2.731181915</v>
+        <v>2.71761798</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7539426331689142</v>
+        <v>0.8401431244329944</v>
       </c>
       <c r="T93">
-        <v>10.95474131877811</v>
+        <v>12.28823550359207</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.588878862615061</v>
+        <v>2.56073887497794</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9063,22 +9063,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1181454099546395</v>
+        <v>0.1180556529240768</v>
       </c>
       <c r="C94">
-        <v>2.723526581389564</v>
+        <v>2.487225836931003</v>
       </c>
       <c r="D94">
-        <v>16.78352658138957</v>
+        <v>16.792225836931</v>
       </c>
       <c r="E94">
-        <v>22.54</v>
+        <v>22.785</v>
       </c>
       <c r="F94">
-        <v>22.54</v>
+        <v>22.785</v>
       </c>
       <c r="G94">
         <v>8.48</v>
@@ -9099,28 +9099,28 @@
         <v>4.15</v>
       </c>
       <c r="M94">
-        <v>1.620626</v>
+        <v>1.6382415</v>
       </c>
       <c r="N94">
-        <v>2.529374</v>
+        <v>2.5117585</v>
       </c>
       <c r="O94">
-        <v>0.5817560199999999</v>
+        <v>0.577704455</v>
       </c>
       <c r="P94">
-        <v>1.94761798</v>
+        <v>1.934054045</v>
       </c>
       <c r="Q94">
-        <v>2.71761798</v>
+        <v>2.704054044999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8401431244329944</v>
+        <v>0.9509723274868116</v>
       </c>
       <c r="T94">
-        <v>12.28823550359207</v>
+        <v>14.0027280269243</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.56073887497794</v>
+        <v>2.533204048365274</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9145,22 +9145,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1180556529240768</v>
+        <v>0.117965895893514</v>
       </c>
       <c r="C95">
-        <v>2.487225836931003</v>
+        <v>2.250934115164061</v>
       </c>
       <c r="D95">
-        <v>16.792225836931</v>
+        <v>16.80093411516406</v>
       </c>
       <c r="E95">
-        <v>22.785</v>
+        <v>23.03</v>
       </c>
       <c r="F95">
-        <v>22.785</v>
+        <v>23.03</v>
       </c>
       <c r="G95">
         <v>8.48</v>
@@ -9181,28 +9181,28 @@
         <v>4.15</v>
       </c>
       <c r="M95">
-        <v>1.6382415</v>
+        <v>1.655857</v>
       </c>
       <c r="N95">
-        <v>2.5117585</v>
+        <v>2.494143</v>
       </c>
       <c r="O95">
-        <v>0.577704455</v>
+        <v>0.5736528900000001</v>
       </c>
       <c r="P95">
-        <v>1.934054045</v>
+        <v>1.92049011</v>
       </c>
       <c r="Q95">
-        <v>2.704054044999999</v>
+        <v>2.69049011</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9509723274868116</v>
+        <v>1.098744598225235</v>
       </c>
       <c r="T95">
-        <v>14.0027280269243</v>
+        <v>16.28871805803394</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.533204048365274</v>
+        <v>2.506255069127346</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9227,22 +9227,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.117965895893514</v>
+        <v>0.1207289888629513</v>
       </c>
       <c r="C96">
-        <v>2.250934115164061</v>
+        <v>1.741932846223769</v>
       </c>
       <c r="D96">
-        <v>16.80093411516406</v>
+        <v>16.53693284622377</v>
       </c>
       <c r="E96">
-        <v>23.03</v>
+        <v>23.275</v>
       </c>
       <c r="F96">
-        <v>23.03</v>
+        <v>23.275</v>
       </c>
       <c r="G96">
         <v>8.48</v>
@@ -9263,45 +9263,45 @@
         <v>4.15</v>
       </c>
       <c r="M96">
-        <v>1.655857</v>
+        <v>1.764245</v>
       </c>
       <c r="N96">
-        <v>2.494143</v>
+        <v>2.385755</v>
       </c>
       <c r="O96">
-        <v>0.5736528900000001</v>
+        <v>0.54872365</v>
       </c>
       <c r="P96">
-        <v>1.92049011</v>
+        <v>1.83703135</v>
       </c>
       <c r="Q96">
-        <v>2.69049011</v>
+        <v>2.60703135</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.098744598225235</v>
+        <v>1.305625777259027</v>
       </c>
       <c r="T96">
-        <v>16.28871805803394</v>
+        <v>19.48910410158744</v>
       </c>
       <c r="U96">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V96">
         <v>0.23</v>
       </c>
       <c r="W96">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y96">
-        <v>2.506255069127346</v>
+        <v>2.352281004055559</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9309,22 +9309,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1207289888629513</v>
+        <v>0.1206692618323885</v>
       </c>
       <c r="C97">
-        <v>1.741932846223769</v>
+        <v>1.502551736001479</v>
       </c>
       <c r="D97">
-        <v>16.53693284622377</v>
+        <v>16.54255173600148</v>
       </c>
       <c r="E97">
-        <v>23.275</v>
+        <v>23.52</v>
       </c>
       <c r="F97">
-        <v>23.275</v>
+        <v>23.52</v>
       </c>
       <c r="G97">
         <v>8.48</v>
@@ -9345,28 +9345,28 @@
         <v>4.15</v>
       </c>
       <c r="M97">
-        <v>1.764245</v>
+        <v>1.782816</v>
       </c>
       <c r="N97">
-        <v>2.385755</v>
+        <v>2.367184</v>
       </c>
       <c r="O97">
-        <v>0.54872365</v>
+        <v>0.54445232</v>
       </c>
       <c r="P97">
-        <v>1.83703135</v>
+        <v>1.82273168</v>
       </c>
       <c r="Q97">
-        <v>2.60703135</v>
+        <v>2.59273168</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.305625777259027</v>
+        <v>1.615947545809716</v>
       </c>
       <c r="T97">
-        <v>19.48910410158744</v>
+        <v>24.28968316691768</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.352281004055559</v>
+        <v>2.32777807692998</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9391,22 +9391,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1206692618323885</v>
+        <v>0.1206095348018258</v>
       </c>
       <c r="C98">
-        <v>1.502551736001482</v>
+        <v>1.263174445429872</v>
       </c>
       <c r="D98">
-        <v>16.54255173600148</v>
+        <v>16.54817444542987</v>
       </c>
       <c r="E98">
-        <v>23.52</v>
+        <v>23.765</v>
       </c>
       <c r="F98">
-        <v>23.52</v>
+        <v>23.765</v>
       </c>
       <c r="G98">
         <v>8.48</v>
@@ -9427,28 +9427,28 @@
         <v>4.15</v>
       </c>
       <c r="M98">
-        <v>1.782816</v>
+        <v>1.801387</v>
       </c>
       <c r="N98">
-        <v>2.367184</v>
+        <v>2.348613</v>
       </c>
       <c r="O98">
-        <v>0.54445232</v>
+        <v>0.5401809900000001</v>
       </c>
       <c r="P98">
-        <v>1.82273168</v>
+        <v>1.80843201</v>
       </c>
       <c r="Q98">
-        <v>2.59273168</v>
+        <v>2.57843201</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.615947545809712</v>
+        <v>2.133150493394191</v>
       </c>
       <c r="T98">
-        <v>24.28968316691762</v>
+        <v>32.29064827580134</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.32777807692998</v>
+        <v>2.303780364796681</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9473,22 +9473,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1206095348018258</v>
+        <v>0.120549807771263</v>
       </c>
       <c r="C99">
-        <v>1.263174445429872</v>
+        <v>1.023800978405106</v>
       </c>
       <c r="D99">
-        <v>16.54817444542987</v>
+        <v>16.5538009784051</v>
       </c>
       <c r="E99">
-        <v>23.765</v>
+        <v>24.01</v>
       </c>
       <c r="F99">
-        <v>23.765</v>
+        <v>24.01</v>
       </c>
       <c r="G99">
         <v>8.48</v>
@@ -9509,28 +9509,28 @@
         <v>4.15</v>
       </c>
       <c r="M99">
-        <v>1.801387</v>
+        <v>1.819958</v>
       </c>
       <c r="N99">
-        <v>2.348613</v>
+        <v>2.330042000000001</v>
       </c>
       <c r="O99">
-        <v>0.5401809900000001</v>
+        <v>0.5359096600000002</v>
       </c>
       <c r="P99">
-        <v>1.80843201</v>
+        <v>1.79413234</v>
       </c>
       <c r="Q99">
-        <v>2.57843201</v>
+        <v>2.56413234</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.133150493394191</v>
+        <v>3.167556388563149</v>
       </c>
       <c r="T99">
-        <v>32.29064827580134</v>
+        <v>48.29257849356876</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.303780364796681</v>
+        <v>2.280272401890594</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9555,22 +9555,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.120549807771263</v>
+        <v>0.1204900807407003</v>
       </c>
       <c r="C100">
-        <v>1.023800978405106</v>
+        <v>0.7844313388286146</v>
       </c>
       <c r="D100">
-        <v>16.5538009784051</v>
+        <v>16.55943133882861</v>
       </c>
       <c r="E100">
-        <v>24.01</v>
+        <v>24.255</v>
       </c>
       <c r="F100">
-        <v>24.01</v>
+        <v>24.255</v>
       </c>
       <c r="G100">
         <v>8.48</v>
@@ -9591,28 +9591,28 @@
         <v>4.15</v>
       </c>
       <c r="M100">
-        <v>1.819958</v>
+        <v>1.838529</v>
       </c>
       <c r="N100">
-        <v>2.330042000000001</v>
+        <v>2.311471</v>
       </c>
       <c r="O100">
-        <v>0.5359096600000002</v>
+        <v>0.53163833</v>
       </c>
       <c r="P100">
-        <v>1.79413234</v>
+        <v>1.77983267</v>
       </c>
       <c r="Q100">
-        <v>2.56413234</v>
+        <v>2.54983267</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.167556388563149</v>
+        <v>6.270774074070023</v>
       </c>
       <c r="T100">
-        <v>48.29257849356876</v>
+        <v>96.29836914687104</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9629,91 +9629,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.280272401890594</v>
+        <v>2.257239347326042</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1204900807407003</v>
-      </c>
-      <c r="C101">
-        <v>0.7844313388286146</v>
-      </c>
-      <c r="D101">
-        <v>16.55943133882861</v>
-      </c>
-      <c r="E101">
-        <v>24.255</v>
-      </c>
-      <c r="F101">
-        <v>24.255</v>
-      </c>
-      <c r="G101">
-        <v>8.48</v>
-      </c>
-      <c r="H101">
-        <v>24.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.92</v>
-      </c>
-      <c r="K101">
-        <v>0.7699999999999996</v>
-      </c>
-      <c r="L101">
-        <v>4.15</v>
-      </c>
-      <c r="M101">
-        <v>1.838529</v>
-      </c>
-      <c r="N101">
-        <v>2.311471</v>
-      </c>
-      <c r="O101">
-        <v>0.53163833</v>
-      </c>
-      <c r="P101">
-        <v>1.77983267</v>
-      </c>
-      <c r="Q101">
-        <v>2.54983267</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.270774074070023</v>
-      </c>
-      <c r="T101">
-        <v>96.29836914687104</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.23</v>
-      </c>
-      <c r="W101">
-        <v>0.05836600000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.257239347326042</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
